--- a/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_production_and_exploration.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0438</v>
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="E2">
+        <v>-0.228</v>
       </c>
       <c r="G2">
-        <v>-0.5276647119696447</v>
+        <v>0.4432926829268292</v>
       </c>
       <c r="H2">
-        <v>-0.5276647119696447</v>
+        <v>0.4432926829268292</v>
       </c>
       <c r="I2">
-        <v>-0.7144106336104271</v>
+        <v>0.2840746054519369</v>
       </c>
       <c r="J2">
-        <v>-0.7144106336104271</v>
+        <v>0.2840746054519369</v>
       </c>
       <c r="K2">
-        <v>-25.685</v>
+        <v>10.439</v>
       </c>
       <c r="L2">
-        <v>-0.8859951707485338</v>
+        <v>0.1872130559540889</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +627,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>49.961</v>
+        <v>40.53700000000001</v>
       </c>
       <c r="V2">
-        <v>0.9041078537821209</v>
+        <v>0.668596404420254</v>
       </c>
       <c r="W2">
-        <v>-0.2539214830970556</v>
+        <v>-0.006453268953268948</v>
       </c>
       <c r="X2">
-        <v>0.07520379584976714</v>
+        <v>0.1480636767965204</v>
       </c>
       <c r="Y2">
-        <v>-0.3291252789468228</v>
+        <v>-0.1545169457497894</v>
       </c>
       <c r="Z2">
-        <v>1.144184568730299</v>
+        <v>2.442828353631824</v>
       </c>
       <c r="AA2">
-        <v>-0.751727261037163</v>
+        <v>0.364100489623947</v>
       </c>
       <c r="AB2">
-        <v>0.06218370455878944</v>
+        <v>0.10339449662276</v>
       </c>
       <c r="AC2">
-        <v>-0.8139109655959526</v>
+        <v>0.260705993001187</v>
       </c>
       <c r="AD2">
-        <v>1.73</v>
+        <v>1.942</v>
       </c>
       <c r="AE2">
-        <v>0.003821341831415753</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.733821341831416</v>
+        <v>1.942</v>
       </c>
       <c r="AG2">
-        <v>-48.22717865816858</v>
+        <v>-38.59500000000001</v>
       </c>
       <c r="AH2">
-        <v>0.03042121586184735</v>
+        <v>0.03103624624432653</v>
       </c>
       <c r="AI2">
-        <v>0.02287549712016567</v>
+        <v>0.01868457512315271</v>
       </c>
       <c r="AJ2">
-        <v>-6.857444020554311</v>
+        <v>-1.751531654186522</v>
       </c>
       <c r="AK2">
-        <v>-1.866895528754101</v>
+        <v>-0.6087635451663277</v>
       </c>
       <c r="AL2">
-        <v>0.006</v>
+        <v>0.109</v>
       </c>
       <c r="AM2">
-        <v>-0.173</v>
+        <v>0.018</v>
       </c>
       <c r="AN2">
-        <v>-0.1134872736814484</v>
+        <v>0.07709102457226788</v>
       </c>
       <c r="AO2">
-        <v>-3452</v>
+        <v>145.3211009174312</v>
       </c>
       <c r="AP2">
-        <v>3.163682672406755</v>
+        <v>-1.532094795760391</v>
       </c>
       <c r="AQ2">
-        <v>119.7225433526012</v>
+        <v>879.9999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New Zealand Energy Corp. (TSXV:NZ)</t>
+          <t>New Zealand Oil &amp; Gas Limited (NZSE:NZO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0258</v>
+        <v>0.177</v>
+      </c>
+      <c r="E3">
+        <v>-0.228</v>
       </c>
       <c r="G3">
-        <v>0.0007712082262210796</v>
+        <v>0.4731800766283524</v>
       </c>
       <c r="H3">
-        <v>0.0007712082262210796</v>
+        <v>0.4731800766283524</v>
       </c>
       <c r="I3">
-        <v>-0.1570088093486589</v>
+        <v>0.3065134099616858</v>
       </c>
       <c r="J3">
-        <v>-0.1570088093486589</v>
+        <v>0.3065134099616858</v>
       </c>
       <c r="K3">
-        <v>-0.285</v>
+        <v>10.7</v>
       </c>
       <c r="L3">
-        <v>-0.07326478149100256</v>
+        <v>0.2049808429118774</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,76 +758,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.5610000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="V3">
-        <v>0.2377118644067797</v>
+        <v>0.6744966442953021</v>
       </c>
       <c r="W3">
-        <v>-0.2175572519083969</v>
+        <v>0.1544011544011544</v>
       </c>
       <c r="X3">
-        <v>0.08684026374685679</v>
+        <v>0.108586187949575</v>
       </c>
       <c r="Y3">
-        <v>-0.3043975156552537</v>
+        <v>0.04581496645157941</v>
       </c>
       <c r="Z3">
-        <v>4.337541736078847</v>
+        <v>2.578159727367018</v>
       </c>
       <c r="AA3">
-        <v>-0.6810322634818546</v>
+        <v>0.790240529461155</v>
       </c>
       <c r="AB3">
-        <v>0.06093229076003324</v>
+        <v>0.1082269328647795</v>
       </c>
       <c r="AC3">
-        <v>-0.7419645542418879</v>
+        <v>0.6820135965963755</v>
       </c>
       <c r="AD3">
-        <v>1.58</v>
+        <v>0.312</v>
       </c>
       <c r="AE3">
-        <v>0.003821341831415753</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.583821341831416</v>
+        <v>0.312</v>
       </c>
       <c r="AG3">
-        <v>1.022821341831416</v>
+        <v>-39.88800000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4015956110973139</v>
+        <v>0.005207637868874349</v>
       </c>
       <c r="AI3">
-        <v>0.50378859662196</v>
+        <v>0.003076558987102118</v>
       </c>
       <c r="AJ3">
-        <v>0.3023574816628281</v>
+        <v>-2.023538961038962</v>
       </c>
       <c r="AK3">
-        <v>0.3960093271903034</v>
+        <v>-0.6516369339345228</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.105</v>
+        <v>-0.091</v>
       </c>
       <c r="AN3">
-        <v>28.21428571428572</v>
+        <v>0.01263157894736842</v>
       </c>
       <c r="AP3">
-        <v>18.26466681841814</v>
+        <v>-1.614898785425102</v>
       </c>
       <c r="AQ3">
-        <v>5.828571428571428</v>
+        <v>-175.8241758241758</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New Zealand Oil &amp; Gas Limited (NZSE:NZO)</t>
+          <t>New Zealand Energy Corp. (TSXV:NZ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,25 +847,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.06179999999999999</v>
+        <v>-0.0868</v>
       </c>
       <c r="G4">
-        <v>-0.6095617529880478</v>
+        <v>0.005056179775280899</v>
       </c>
       <c r="H4">
-        <v>-0.6095617529880478</v>
+        <v>0.005056179775280899</v>
       </c>
       <c r="I4">
-        <v>-0.800796812749004</v>
+        <v>-0.0449438202247191</v>
       </c>
       <c r="J4">
-        <v>-0.800796812749004</v>
+        <v>-0.0449438202247191</v>
       </c>
       <c r="K4">
-        <v>-25.4</v>
+        <v>-0.261</v>
       </c>
       <c r="L4">
-        <v>-1.01195219123506</v>
+        <v>-0.07331460674157303</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +889,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>49.4</v>
+        <v>0.337</v>
       </c>
       <c r="V4">
-        <v>0.9338374291115312</v>
+        <v>0.3271844660194175</v>
       </c>
       <c r="W4">
-        <v>-0.2902857142857143</v>
+        <v>-0.1673076923076923</v>
       </c>
       <c r="X4">
-        <v>0.0635673279526775</v>
+        <v>0.1875411656434658</v>
       </c>
       <c r="Y4">
-        <v>-0.3538530422383918</v>
+        <v>-0.3548488579511582</v>
       </c>
       <c r="Z4">
-        <v>1.027004909983634</v>
+        <v>1.380379992245056</v>
       </c>
       <c r="AA4">
-        <v>-0.8224222585924715</v>
+        <v>-0.06203955021326095</v>
       </c>
       <c r="AB4">
-        <v>0.06343511835754563</v>
+        <v>0.09856206038074054</v>
       </c>
       <c r="AC4">
-        <v>-0.8858573769500172</v>
+        <v>-0.1606016105940015</v>
       </c>
       <c r="AD4">
-        <v>0.15</v>
+        <v>1.63</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.15</v>
+        <v>1.63</v>
       </c>
       <c r="AG4">
-        <v>-49.25</v>
+        <v>1.293</v>
       </c>
       <c r="AH4">
-        <v>0.002827521206409048</v>
+        <v>0.612781954887218</v>
       </c>
       <c r="AI4">
-        <v>0.002064693737095664</v>
+        <v>0.6458003169572107</v>
       </c>
       <c r="AJ4">
-        <v>-13.49315068493151</v>
+        <v>0.5566078346965131</v>
       </c>
       <c r="AK4">
-        <v>-2.118279569892473</v>
+        <v>0.5912208504801097</v>
       </c>
       <c r="AL4">
-        <v>0.006</v>
+        <v>0.109</v>
       </c>
       <c r="AM4">
-        <v>-0.06799999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="AN4">
-        <v>-0.009803921568627451</v>
+        <v>3.319755600814664</v>
       </c>
       <c r="AO4">
-        <v>-3350</v>
+        <v>-1.467889908256881</v>
       </c>
       <c r="AP4">
-        <v>3.218954248366013</v>
+        <v>2.633401221995927</v>
       </c>
       <c r="AQ4">
-        <v>295.5882352941177</v>
+        <v>-1.467889908256881</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_production_and_exploration.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04509999999999999</v>
+        <v>-0.0175</v>
       </c>
       <c r="E2">
-        <v>-0.228</v>
+        <v>0.698</v>
       </c>
       <c r="G2">
-        <v>0.4432926829268292</v>
+        <v>0.4458506888817687</v>
       </c>
       <c r="H2">
-        <v>0.4432926829268292</v>
+        <v>0.4458506888817687</v>
       </c>
       <c r="I2">
-        <v>0.2840746054519369</v>
+        <v>0.2552066645305991</v>
       </c>
       <c r="J2">
-        <v>0.2840746054519369</v>
+        <v>0.2326514276301835</v>
       </c>
       <c r="K2">
-        <v>10.439</v>
+        <v>6.849</v>
       </c>
       <c r="L2">
-        <v>0.1872130559540889</v>
+        <v>0.1097244472925344</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +633,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>40.53700000000001</v>
+        <v>22.368</v>
       </c>
       <c r="V2">
-        <v>0.668596404420254</v>
+        <v>0.3959638874137016</v>
       </c>
       <c r="W2">
-        <v>-0.006453268953268948</v>
+        <v>0.1804762077513755</v>
       </c>
       <c r="X2">
-        <v>0.1480636767965204</v>
+        <v>0.08925626378281272</v>
       </c>
       <c r="Y2">
-        <v>-0.1545169457497894</v>
+        <v>0.0912199439685628</v>
       </c>
       <c r="Z2">
-        <v>2.442828353631824</v>
+        <v>1.139071880873739</v>
       </c>
       <c r="AA2">
-        <v>0.364100489623947</v>
+        <v>0.1312553029962081</v>
       </c>
       <c r="AB2">
-        <v>0.10339449662276</v>
+        <v>0.08123099072002843</v>
       </c>
       <c r="AC2">
-        <v>0.260705993001187</v>
+        <v>0.05002431227617968</v>
       </c>
       <c r="AD2">
-        <v>1.942</v>
+        <v>2.124</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.942</v>
+        <v>2.124</v>
       </c>
       <c r="AG2">
-        <v>-38.59500000000001</v>
+        <v>-20.244</v>
       </c>
       <c r="AH2">
-        <v>0.03103624624432653</v>
+        <v>0.03623707646637322</v>
       </c>
       <c r="AI2">
-        <v>0.01868457512315271</v>
+        <v>0.01871959387999718</v>
       </c>
       <c r="AJ2">
-        <v>-1.751531654186522</v>
+        <v>-0.5585168018539979</v>
       </c>
       <c r="AK2">
-        <v>-0.6087635451663277</v>
+        <v>-0.2222271010801792</v>
       </c>
       <c r="AL2">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.018</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.07709102457226788</v>
-      </c>
-      <c r="AO2">
-        <v>145.3211009174312</v>
+        <v>0.07924781732706515</v>
       </c>
       <c r="AP2">
-        <v>-1.532094795760391</v>
+        <v>-0.7553167674054176</v>
       </c>
       <c r="AQ2">
-        <v>879.9999999999999</v>
+        <v>-23.25547445255474</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +716,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.177</v>
+        <v>0.225</v>
       </c>
       <c r="E3">
-        <v>-0.228</v>
+        <v>0.698</v>
       </c>
       <c r="G3">
-        <v>0.4731800766283524</v>
+        <v>0.431404958677686</v>
       </c>
       <c r="H3">
-        <v>0.4731800766283524</v>
+        <v>0.431404958677686</v>
       </c>
       <c r="I3">
-        <v>0.3065134099616858</v>
+        <v>0.2628099173553719</v>
       </c>
       <c r="J3">
-        <v>0.3065134099616858</v>
+        <v>0.2163554883017111</v>
       </c>
       <c r="K3">
-        <v>10.7</v>
+        <v>6.59</v>
       </c>
       <c r="L3">
-        <v>0.2049808429118774</v>
+        <v>0.1089256198347107</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,70 +761,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>40.2</v>
+        <v>22.3</v>
       </c>
       <c r="V3">
-        <v>0.6744966442953021</v>
+        <v>0.4305019305019305</v>
       </c>
       <c r="W3">
-        <v>0.1544011544011544</v>
+        <v>0.07124324324324324</v>
       </c>
       <c r="X3">
-        <v>0.108586187949575</v>
+        <v>0.08324290613948956</v>
       </c>
       <c r="Y3">
-        <v>0.04581496645157941</v>
+        <v>-0.01199966289624632</v>
       </c>
       <c r="Z3">
-        <v>2.578159727367018</v>
+        <v>1.149927773131605</v>
       </c>
       <c r="AA3">
-        <v>0.790240529461155</v>
+        <v>0.2487931848675877</v>
       </c>
       <c r="AB3">
-        <v>0.1082269328647795</v>
+        <v>0.08292706179620826</v>
       </c>
       <c r="AC3">
-        <v>0.6820135965963755</v>
+        <v>0.1658661230713794</v>
       </c>
       <c r="AD3">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AG3">
-        <v>-39.88800000000001</v>
+        <v>-21.976</v>
       </c>
       <c r="AH3">
-        <v>0.005207637868874349</v>
+        <v>0.006215946588903385</v>
       </c>
       <c r="AI3">
-        <v>0.003076558987102118</v>
+        <v>0.002934144751141057</v>
       </c>
       <c r="AJ3">
-        <v>-2.023538961038962</v>
+        <v>-0.7368562231759657</v>
       </c>
       <c r="AK3">
-        <v>-0.6516369339345228</v>
+        <v>-0.2493758794426036</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.091</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.01263157894736842</v>
+        <v>0.01241379310344828</v>
       </c>
       <c r="AP3">
-        <v>-1.614898785425102</v>
+        <v>-0.8419923371647509</v>
       </c>
       <c r="AQ3">
-        <v>-175.8241758241758</v>
+        <v>-23.21167883211679</v>
       </c>
     </row>
     <row r="4">
@@ -847,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0868</v>
+        <v>-0.26</v>
       </c>
       <c r="G4">
-        <v>0.005056179775280899</v>
+        <v>0.9010416666666667</v>
       </c>
       <c r="H4">
-        <v>0.005056179775280899</v>
+        <v>0.9010416666666667</v>
       </c>
       <c r="I4">
-        <v>-0.0449438202247191</v>
+        <v>0.015625</v>
       </c>
       <c r="J4">
-        <v>-0.0449438202247191</v>
+        <v>0.015625</v>
       </c>
       <c r="K4">
-        <v>-0.261</v>
+        <v>0.259</v>
       </c>
       <c r="L4">
-        <v>-0.07331460674157303</v>
+        <v>0.1348958333333334</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,7 +871,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,79 +880,73 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.337</v>
+        <v>0.068</v>
       </c>
       <c r="V4">
-        <v>0.3271844660194175</v>
+        <v>0.01449893390191898</v>
       </c>
       <c r="W4">
-        <v>-0.1673076923076923</v>
+        <v>0.2897091722595078</v>
       </c>
       <c r="X4">
-        <v>0.1875411656434658</v>
+        <v>0.09526962142613588</v>
       </c>
       <c r="Y4">
-        <v>-0.3548488579511582</v>
+        <v>0.1944395508333719</v>
       </c>
       <c r="Z4">
-        <v>1.380379992245056</v>
+        <v>0.8779149519890261</v>
       </c>
       <c r="AA4">
-        <v>-0.06203955021326095</v>
+        <v>0.01371742112482853</v>
       </c>
       <c r="AB4">
-        <v>0.09856206038074054</v>
+        <v>0.07953491964384858</v>
       </c>
       <c r="AC4">
-        <v>-0.1606016105940015</v>
+        <v>-0.06581749851902005</v>
       </c>
       <c r="AD4">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>1.293</v>
+        <v>1.732</v>
       </c>
       <c r="AH4">
-        <v>0.612781954887218</v>
+        <v>0.2773497688751926</v>
       </c>
       <c r="AI4">
-        <v>0.6458003169572107</v>
+        <v>0.5921052631578947</v>
       </c>
       <c r="AJ4">
-        <v>0.5566078346965131</v>
+        <v>0.2696979134226097</v>
       </c>
       <c r="AK4">
-        <v>0.5912208504801097</v>
+        <v>0.5827725437415882</v>
       </c>
       <c r="AL4">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>3.319755600814664</v>
-      </c>
-      <c r="AO4">
-        <v>-1.467889908256881</v>
+        <v>2.564102564102564</v>
       </c>
       <c r="AP4">
-        <v>2.633401221995927</v>
-      </c>
-      <c r="AQ4">
-        <v>-1.467889908256881</v>
+        <v>2.467236467236468</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_production_and_exploration.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08744674570503419</v>
+        <v>0.0872342948170601</v>
       </c>
       <c r="C2">
-        <v>72.46102699644794</v>
+        <v>71.88927751737384</v>
       </c>
       <c r="D2">
-        <v>46.66102699644794</v>
+        <v>46.90027751737383</v>
       </c>
       <c r="E2">
-        <v>-33.3</v>
+        <v>-32.489</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8109999999999999</v>
       </c>
       <c r="G2">
         <v>25.8</v>
@@ -1573,28 +1573,28 @@
         <v>18.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0407933</v>
       </c>
       <c r="N2">
-        <v>18.8</v>
+        <v>18.7592067</v>
       </c>
       <c r="O2">
-        <v>5.264000000000001</v>
+        <v>5.252577876</v>
       </c>
       <c r="P2">
-        <v>13.536</v>
+        <v>13.506628824</v>
       </c>
       <c r="Q2">
-        <v>23.836</v>
+        <v>23.806628824</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08744674570503419</v>
+        <v>0.08774963112834354</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9688136519247931</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>460.8599941657086</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0872342948170601</v>
+        <v>0.087021843929086</v>
       </c>
       <c r="C3">
-        <v>71.88927751737384</v>
+        <v>71.31999415726843</v>
       </c>
       <c r="D3">
-        <v>46.90027751737383</v>
+        <v>47.14199415726842</v>
       </c>
       <c r="E3">
-        <v>-32.489</v>
+        <v>-31.678</v>
       </c>
       <c r="F3">
-        <v>0.8109999999999999</v>
+        <v>1.622</v>
       </c>
       <c r="G3">
         <v>25.8</v>
@@ -1655,28 +1655,28 @@
         <v>18.8</v>
       </c>
       <c r="M3">
-        <v>0.0407933</v>
+        <v>0.0815866</v>
       </c>
       <c r="N3">
-        <v>18.7592067</v>
+        <v>18.7184134</v>
       </c>
       <c r="O3">
-        <v>5.252577876</v>
+        <v>5.241155752</v>
       </c>
       <c r="P3">
-        <v>13.506628824</v>
+        <v>13.477257648</v>
       </c>
       <c r="Q3">
-        <v>23.806628824</v>
+        <v>23.777257648</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08774963112834354</v>
+        <v>0.08805869788682245</v>
       </c>
       <c r="T3">
-        <v>0.9688136519247931</v>
+        <v>0.9759514523515578</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>460.8599941657086</v>
+        <v>230.4299970828543</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.087021843929086</v>
+        <v>0.0868093930411119</v>
       </c>
       <c r="C4">
-        <v>71.31999415726843</v>
+        <v>70.75321524363127</v>
       </c>
       <c r="D4">
-        <v>47.14199415726842</v>
+        <v>47.38621524363127</v>
       </c>
       <c r="E4">
-        <v>-31.678</v>
+        <v>-30.867</v>
       </c>
       <c r="F4">
-        <v>1.622</v>
+        <v>2.433</v>
       </c>
       <c r="G4">
         <v>25.8</v>
@@ -1737,28 +1737,28 @@
         <v>18.8</v>
       </c>
       <c r="M4">
-        <v>0.0815866</v>
+        <v>0.1223799</v>
       </c>
       <c r="N4">
-        <v>18.7184134</v>
+        <v>18.6776201</v>
       </c>
       <c r="O4">
-        <v>5.241155752</v>
+        <v>5.229733628000001</v>
       </c>
       <c r="P4">
-        <v>13.477257648</v>
+        <v>13.447886472</v>
       </c>
       <c r="Q4">
-        <v>23.777257648</v>
+        <v>23.747886472</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08805869788682245</v>
+        <v>0.08837413715578547</v>
       </c>
       <c r="T4">
-        <v>0.9759514523515578</v>
+        <v>0.9832364239211426</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>230.4299970828543</v>
+        <v>153.6199980552362</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0868093930411119</v>
+        <v>0.08659694215313782</v>
       </c>
       <c r="C5">
-        <v>70.75321524363127</v>
+        <v>70.18897990232681</v>
       </c>
       <c r="D5">
-        <v>47.38621524363127</v>
+        <v>47.63297990232681</v>
       </c>
       <c r="E5">
-        <v>-30.867</v>
+        <v>-30.056</v>
       </c>
       <c r="F5">
-        <v>2.433</v>
+        <v>3.244</v>
       </c>
       <c r="G5">
         <v>25.8</v>
@@ -1819,28 +1819,28 @@
         <v>18.8</v>
       </c>
       <c r="M5">
-        <v>0.1223799</v>
+        <v>0.1631732</v>
       </c>
       <c r="N5">
-        <v>18.6776201</v>
+        <v>18.6368268</v>
       </c>
       <c r="O5">
-        <v>5.229733628000001</v>
+        <v>5.218311504000001</v>
       </c>
       <c r="P5">
-        <v>13.447886472</v>
+        <v>13.418515296</v>
       </c>
       <c r="Q5">
-        <v>23.747886472</v>
+        <v>23.718515296</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08837413715578547</v>
+        <v>0.08869614807618523</v>
       </c>
       <c r="T5">
-        <v>0.9832364239211426</v>
+        <v>0.9906731657317603</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>153.6199980552362</v>
+        <v>115.2149985414272</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08659694215313782</v>
+        <v>0.0863844912651637</v>
       </c>
       <c r="C6">
-        <v>70.18897990232681</v>
+        <v>69.6273280784807</v>
       </c>
       <c r="D6">
-        <v>47.63297990232681</v>
+        <v>47.88232807848071</v>
       </c>
       <c r="E6">
-        <v>-30.056</v>
+        <v>-29.245</v>
       </c>
       <c r="F6">
-        <v>3.244</v>
+        <v>4.055</v>
       </c>
       <c r="G6">
         <v>25.8</v>
@@ -1901,28 +1901,28 @@
         <v>18.8</v>
       </c>
       <c r="M6">
-        <v>0.1631732</v>
+        <v>0.2039665</v>
       </c>
       <c r="N6">
-        <v>18.6368268</v>
+        <v>18.5960335</v>
       </c>
       <c r="O6">
-        <v>5.218311504000001</v>
+        <v>5.206889380000001</v>
       </c>
       <c r="P6">
-        <v>13.418515296</v>
+        <v>13.38914412</v>
       </c>
       <c r="Q6">
-        <v>23.718515296</v>
+        <v>23.68914412</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08869614807618523</v>
+        <v>0.08902493817385654</v>
       </c>
       <c r="T6">
-        <v>0.9906731657317603</v>
+        <v>0.9982664705278648</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>115.2149985414272</v>
+        <v>92.17199883314173</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0863844912651637</v>
+        <v>0.08617204037718962</v>
       </c>
       <c r="C7">
-        <v>69.6273280784807</v>
+        <v>69.06830055803583</v>
       </c>
       <c r="D7">
-        <v>47.88232807848071</v>
+        <v>48.13430055803583</v>
       </c>
       <c r="E7">
-        <v>-29.245</v>
+        <v>-28.434</v>
       </c>
       <c r="F7">
-        <v>4.055</v>
+        <v>4.866</v>
       </c>
       <c r="G7">
         <v>25.8</v>
@@ -1983,28 +1983,28 @@
         <v>18.8</v>
       </c>
       <c r="M7">
-        <v>0.2039665</v>
+        <v>0.2447598</v>
       </c>
       <c r="N7">
-        <v>18.5960335</v>
+        <v>18.5552402</v>
       </c>
       <c r="O7">
-        <v>5.206889380000001</v>
+        <v>5.195467256000001</v>
       </c>
       <c r="P7">
-        <v>13.38914412</v>
+        <v>13.359772944</v>
       </c>
       <c r="Q7">
-        <v>23.68914412</v>
+        <v>23.659772944</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08902493817385654</v>
+        <v>0.08936072380552088</v>
       </c>
       <c r="T7">
-        <v>0.9982664705278648</v>
+        <v>1.006021335000482</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>92.17199883314173</v>
+        <v>76.8099990276181</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08617204037718962</v>
+        <v>0.08595958948921552</v>
       </c>
       <c r="C8">
-        <v>69.06830055803583</v>
+        <v>68.51193898999274</v>
       </c>
       <c r="D8">
-        <v>48.13430055803583</v>
+        <v>48.38893898999273</v>
       </c>
       <c r="E8">
-        <v>-28.434</v>
+        <v>-27.623</v>
       </c>
       <c r="F8">
-        <v>4.866</v>
+        <v>5.676999999999999</v>
       </c>
       <c r="G8">
         <v>25.8</v>
@@ -2065,28 +2065,28 @@
         <v>18.8</v>
       </c>
       <c r="M8">
-        <v>0.2447598</v>
+        <v>0.2855530999999999</v>
       </c>
       <c r="N8">
-        <v>18.5552402</v>
+        <v>18.5144469</v>
       </c>
       <c r="O8">
-        <v>5.195467256000001</v>
+        <v>5.184045132</v>
       </c>
       <c r="P8">
-        <v>13.359772944</v>
+        <v>13.330401768</v>
       </c>
       <c r="Q8">
-        <v>23.659772944</v>
+        <v>23.630401768</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08936072380552088</v>
+        <v>0.08970373063356507</v>
       </c>
       <c r="T8">
-        <v>1.006021335000482</v>
+        <v>1.01394297075208</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>76.8099990276181</v>
+        <v>65.83714202367267</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08595958948921552</v>
+        <v>0.08574713860124145</v>
       </c>
       <c r="C9">
-        <v>68.51193898999273</v>
+        <v>67.95828590935952</v>
       </c>
       <c r="D9">
-        <v>48.38893898999273</v>
+        <v>48.64628590935951</v>
       </c>
       <c r="E9">
-        <v>-27.623</v>
+        <v>-26.812</v>
       </c>
       <c r="F9">
-        <v>5.677</v>
+        <v>6.488</v>
       </c>
       <c r="G9">
         <v>25.8</v>
@@ -2147,28 +2147,28 @@
         <v>18.8</v>
       </c>
       <c r="M9">
-        <v>0.2855531</v>
+        <v>0.3263464</v>
       </c>
       <c r="N9">
-        <v>18.5144469</v>
+        <v>18.4736536</v>
       </c>
       <c r="O9">
-        <v>5.184045132</v>
+        <v>5.172623008000001</v>
       </c>
       <c r="P9">
-        <v>13.330401768</v>
+        <v>13.301030592</v>
       </c>
       <c r="Q9">
-        <v>23.630401768</v>
+        <v>23.601030592</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08970373063356507</v>
+        <v>0.09005419413178417</v>
       </c>
       <c r="T9">
-        <v>1.01394297075208</v>
+        <v>1.02203681597654</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>65.83714202367266</v>
+        <v>57.60749927071358</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08574713860124145</v>
+        <v>0.08553468771326735</v>
       </c>
       <c r="C10">
-        <v>67.95828590935952</v>
+        <v>67.4073847608382</v>
       </c>
       <c r="D10">
-        <v>48.64628590935951</v>
+        <v>48.9063847608382</v>
       </c>
       <c r="E10">
-        <v>-26.812</v>
+        <v>-26.001</v>
       </c>
       <c r="F10">
-        <v>6.488</v>
+        <v>7.298999999999999</v>
       </c>
       <c r="G10">
         <v>25.8</v>
@@ -2229,28 +2229,28 @@
         <v>18.8</v>
       </c>
       <c r="M10">
-        <v>0.3263464</v>
+        <v>0.3671397</v>
       </c>
       <c r="N10">
-        <v>18.4736536</v>
+        <v>18.4328603</v>
       </c>
       <c r="O10">
-        <v>5.172623008000001</v>
+        <v>5.161200884000001</v>
       </c>
       <c r="P10">
-        <v>13.301030592</v>
+        <v>13.271659416</v>
       </c>
       <c r="Q10">
-        <v>23.601030592</v>
+        <v>23.571659416</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09005419413178417</v>
+        <v>0.0904123601244696</v>
       </c>
       <c r="T10">
-        <v>1.02203681597654</v>
+        <v>1.030308547909229</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>57.60749927071358</v>
+        <v>51.20666601841207</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08553468771326735</v>
+        <v>0.08532223682529325</v>
       </c>
       <c r="C11">
-        <v>67.4073847608382</v>
+        <v>66.8592799232748</v>
       </c>
       <c r="D11">
-        <v>48.9063847608382</v>
+        <v>49.1692799232748</v>
       </c>
       <c r="E11">
-        <v>-26.001</v>
+        <v>-25.19</v>
       </c>
       <c r="F11">
-        <v>7.298999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G11">
         <v>25.8</v>
@@ -2311,28 +2311,28 @@
         <v>18.8</v>
       </c>
       <c r="M11">
-        <v>0.3671397</v>
+        <v>0.4079329999999999</v>
       </c>
       <c r="N11">
-        <v>18.4328603</v>
+        <v>18.392067</v>
       </c>
       <c r="O11">
-        <v>5.161200884000001</v>
+        <v>5.149778760000001</v>
       </c>
       <c r="P11">
-        <v>13.271659416</v>
+        <v>13.24228824</v>
       </c>
       <c r="Q11">
-        <v>23.571659416</v>
+        <v>23.54228824</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0904123601244696</v>
+        <v>0.09077848536143693</v>
       </c>
       <c r="T11">
-        <v>1.030308547909229</v>
+        <v>1.038764096107089</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>51.20666601841207</v>
+        <v>46.08599941657086</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08532223682529325</v>
+        <v>0.08510978593731915</v>
       </c>
       <c r="C12">
-        <v>66.8592799232748</v>
+        <v>66.3140167349024</v>
       </c>
       <c r="D12">
-        <v>49.1692799232748</v>
+        <v>49.4350167349024</v>
       </c>
       <c r="E12">
-        <v>-25.19</v>
+        <v>-24.379</v>
       </c>
       <c r="F12">
-        <v>8.109999999999999</v>
+        <v>8.920999999999999</v>
       </c>
       <c r="G12">
         <v>25.8</v>
@@ -2393,28 +2393,28 @@
         <v>18.8</v>
       </c>
       <c r="M12">
-        <v>0.4079329999999999</v>
+        <v>0.4487263</v>
       </c>
       <c r="N12">
-        <v>18.392067</v>
+        <v>18.3512737</v>
       </c>
       <c r="O12">
-        <v>5.149778760000001</v>
+        <v>5.138356636</v>
       </c>
       <c r="P12">
-        <v>13.24228824</v>
+        <v>13.212917064</v>
       </c>
       <c r="Q12">
-        <v>23.54228824</v>
+        <v>23.512917064</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09077848536143693</v>
+        <v>0.09115283813181926</v>
       </c>
       <c r="T12">
-        <v>1.038764096107089</v>
+        <v>1.047409656624001</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>46.08599941657086</v>
+        <v>41.89636310597351</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08510978593731915</v>
+        <v>0.08489733504934505</v>
       </c>
       <c r="C13">
-        <v>66.3140167349024</v>
+        <v>65.77164151940725</v>
       </c>
       <c r="D13">
-        <v>49.4350167349024</v>
+        <v>49.70364151940726</v>
       </c>
       <c r="E13">
-        <v>-24.379</v>
+        <v>-23.568</v>
       </c>
       <c r="F13">
-        <v>8.920999999999999</v>
+        <v>9.731999999999999</v>
       </c>
       <c r="G13">
         <v>25.8</v>
@@ -2475,28 +2475,28 @@
         <v>18.8</v>
       </c>
       <c r="M13">
-        <v>0.4487263</v>
+        <v>0.4895195999999999</v>
       </c>
       <c r="N13">
-        <v>18.3512737</v>
+        <v>18.3104804</v>
       </c>
       <c r="O13">
-        <v>5.138356636</v>
+        <v>5.126934512</v>
       </c>
       <c r="P13">
-        <v>13.212917064</v>
+        <v>13.183545888</v>
       </c>
       <c r="Q13">
-        <v>23.512917064</v>
+        <v>23.483545888</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09115283813181926</v>
+        <v>0.09153569891971028</v>
       </c>
       <c r="T13">
-        <v>1.047409656624001</v>
+        <v>1.056251707152662</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>41.89636310597351</v>
+        <v>38.40499951380905</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08489733504934505</v>
+        <v>0.08468488416137096</v>
       </c>
       <c r="C14">
-        <v>65.77164151940725</v>
+        <v>65.23220161284928</v>
       </c>
       <c r="D14">
-        <v>49.70364151940726</v>
+        <v>49.97520161284928</v>
       </c>
       <c r="E14">
-        <v>-23.568</v>
+        <v>-22.757</v>
       </c>
       <c r="F14">
-        <v>9.731999999999999</v>
+        <v>10.543</v>
       </c>
       <c r="G14">
         <v>25.8</v>
@@ -2557,28 +2557,28 @@
         <v>18.8</v>
       </c>
       <c r="M14">
-        <v>0.4895195999999999</v>
+        <v>0.5303129</v>
       </c>
       <c r="N14">
-        <v>18.3104804</v>
+        <v>18.2696871</v>
       </c>
       <c r="O14">
-        <v>5.126934512</v>
+        <v>5.115512388000001</v>
       </c>
       <c r="P14">
-        <v>13.183545888</v>
+        <v>13.154174712</v>
       </c>
       <c r="Q14">
-        <v>23.483545888</v>
+        <v>23.454174712</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09153569891971028</v>
+        <v>0.09192736110502409</v>
       </c>
       <c r="T14">
-        <v>1.056251707152662</v>
+        <v>1.065297023210718</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>38.40499951380905</v>
+        <v>35.45076878197759</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08468488416137096</v>
+        <v>0.08447243327339686</v>
       </c>
       <c r="C15">
-        <v>65.23220161284928</v>
+        <v>64.69574539146996</v>
       </c>
       <c r="D15">
-        <v>49.97520161284928</v>
+        <v>50.24974539146995</v>
       </c>
       <c r="E15">
-        <v>-22.757</v>
+        <v>-21.946</v>
       </c>
       <c r="F15">
-        <v>10.543</v>
+        <v>11.354</v>
       </c>
       <c r="G15">
         <v>25.8</v>
@@ -2639,28 +2639,28 @@
         <v>18.8</v>
       </c>
       <c r="M15">
-        <v>0.5303129</v>
+        <v>0.5711062</v>
       </c>
       <c r="N15">
-        <v>18.2696871</v>
+        <v>18.2288938</v>
       </c>
       <c r="O15">
-        <v>5.115512388000001</v>
+        <v>5.104090264000001</v>
       </c>
       <c r="P15">
-        <v>13.154174712</v>
+        <v>13.124803536</v>
       </c>
       <c r="Q15">
-        <v>23.454174712</v>
+        <v>23.424803536</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09192736110502409</v>
+        <v>0.09232813171325216</v>
       </c>
       <c r="T15">
-        <v>1.065297023210718</v>
+        <v>1.07455269545617</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>35.45076878197759</v>
+        <v>32.91857101183633</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08447243327339686</v>
+        <v>0.08425998238542276</v>
       </c>
       <c r="C16">
-        <v>64.69574539146996</v>
+        <v>64.16232230042185</v>
       </c>
       <c r="D16">
-        <v>50.24974539146995</v>
+        <v>50.52732230042185</v>
       </c>
       <c r="E16">
-        <v>-21.946</v>
+        <v>-21.135</v>
       </c>
       <c r="F16">
-        <v>11.354</v>
+        <v>12.165</v>
       </c>
       <c r="G16">
         <v>25.8</v>
@@ -2721,28 +2721,28 @@
         <v>18.8</v>
       </c>
       <c r="M16">
-        <v>0.5711062</v>
+        <v>0.6118995</v>
       </c>
       <c r="N16">
-        <v>18.2288938</v>
+        <v>18.1881005</v>
       </c>
       <c r="O16">
-        <v>5.104090264000001</v>
+        <v>5.092668140000001</v>
       </c>
       <c r="P16">
-        <v>13.124803536</v>
+        <v>13.09543236</v>
       </c>
       <c r="Q16">
-        <v>23.424803536</v>
+        <v>23.39543236</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09232813171325216</v>
+        <v>0.09273833221814443</v>
       </c>
       <c r="T16">
-        <v>1.07455269545617</v>
+        <v>1.084026148225044</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>32.91857101183633</v>
+        <v>30.72399961104724</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08425998238542276</v>
+        <v>0.08404753149744866</v>
       </c>
       <c r="C17">
-        <v>64.16232230042186</v>
+        <v>63.63198288345568</v>
       </c>
       <c r="D17">
-        <v>50.52732230042185</v>
+        <v>50.80798288345567</v>
       </c>
       <c r="E17">
-        <v>-21.135</v>
+        <v>-20.324</v>
       </c>
       <c r="F17">
-        <v>12.165</v>
+        <v>12.976</v>
       </c>
       <c r="G17">
         <v>25.8</v>
@@ -2803,28 +2803,28 @@
         <v>18.8</v>
       </c>
       <c r="M17">
-        <v>0.6118994999999999</v>
+        <v>0.6526928</v>
       </c>
       <c r="N17">
-        <v>18.1881005</v>
+        <v>18.1473072</v>
       </c>
       <c r="O17">
-        <v>5.092668140000001</v>
+        <v>5.081246016000001</v>
       </c>
       <c r="P17">
-        <v>13.09543236</v>
+        <v>13.066061184</v>
       </c>
       <c r="Q17">
-        <v>23.39543236</v>
+        <v>23.366061184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09273833221814443</v>
+        <v>0.0931582994017246</v>
       </c>
       <c r="T17">
-        <v>1.084026148225044</v>
+        <v>1.093725159393178</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>30.72399961104724</v>
+        <v>28.80374963535679</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08404753149744866</v>
+        <v>0.08383508060947456</v>
       </c>
       <c r="C18">
-        <v>63.63198288345568</v>
+        <v>63.10477881360217</v>
       </c>
       <c r="D18">
-        <v>50.80798288345567</v>
+        <v>51.09177881360218</v>
       </c>
       <c r="E18">
-        <v>-20.324</v>
+        <v>-19.513</v>
       </c>
       <c r="F18">
-        <v>12.976</v>
+        <v>13.787</v>
       </c>
       <c r="G18">
         <v>25.8</v>
@@ -2885,28 +2885,28 @@
         <v>18.8</v>
       </c>
       <c r="M18">
-        <v>0.6526928</v>
+        <v>0.6934861</v>
       </c>
       <c r="N18">
-        <v>18.1473072</v>
+        <v>18.1065139</v>
       </c>
       <c r="O18">
-        <v>5.081246016000001</v>
+        <v>5.069823892</v>
       </c>
       <c r="P18">
-        <v>13.066061184</v>
+        <v>13.036690008</v>
       </c>
       <c r="Q18">
-        <v>23.366061184</v>
+        <v>23.336690008</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0931582994017246</v>
+        <v>0.09358838627647538</v>
       </c>
       <c r="T18">
-        <v>1.093725159393178</v>
+        <v>1.103657881673796</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>28.80374963535679</v>
+        <v>27.10941142151227</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08383508060947456</v>
+        <v>0.08362262972150047</v>
       </c>
       <c r="C19">
-        <v>63.10477881360217</v>
+        <v>62.58076292488821</v>
       </c>
       <c r="D19">
-        <v>51.09177881360218</v>
+        <v>51.3787629248882</v>
       </c>
       <c r="E19">
-        <v>-19.513</v>
+        <v>-18.702</v>
       </c>
       <c r="F19">
-        <v>13.787</v>
+        <v>14.598</v>
       </c>
       <c r="G19">
         <v>25.8</v>
@@ -2967,28 +2967,28 @@
         <v>18.8</v>
       </c>
       <c r="M19">
-        <v>0.6934861</v>
+        <v>0.7342794</v>
       </c>
       <c r="N19">
-        <v>18.1065139</v>
+        <v>18.0657206</v>
       </c>
       <c r="O19">
-        <v>5.069823892</v>
+        <v>5.058401768000001</v>
       </c>
       <c r="P19">
-        <v>13.036690008</v>
+        <v>13.007318832</v>
       </c>
       <c r="Q19">
-        <v>23.336690008</v>
+        <v>23.307318832</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09358838627647538</v>
+        <v>0.09402896307500058</v>
       </c>
       <c r="T19">
-        <v>1.103657881673796</v>
+        <v>1.113832865473454</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>27.10941142151227</v>
+        <v>25.60333300920604</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08362262972150049</v>
+        <v>0.08341017883352639</v>
       </c>
       <c r="C20">
-        <v>62.58076292488819</v>
+        <v>62.05998924512766</v>
       </c>
       <c r="D20">
-        <v>51.37876292488819</v>
+        <v>51.66898924512766</v>
       </c>
       <c r="E20">
-        <v>-18.702</v>
+        <v>-17.891</v>
       </c>
       <c r="F20">
-        <v>14.598</v>
+        <v>15.409</v>
       </c>
       <c r="G20">
         <v>25.8</v>
@@ -3049,28 +3049,28 @@
         <v>18.8</v>
       </c>
       <c r="M20">
-        <v>0.7342793999999999</v>
+        <v>0.7750726999999999</v>
       </c>
       <c r="N20">
-        <v>18.0657206</v>
+        <v>18.0249273</v>
       </c>
       <c r="O20">
-        <v>5.058401768000001</v>
+        <v>5.046979644000001</v>
       </c>
       <c r="P20">
-        <v>13.007318832</v>
+        <v>12.977947656</v>
       </c>
       <c r="Q20">
-        <v>23.307318832</v>
+        <v>23.277947656</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09402896307500058</v>
+        <v>0.09448041831299553</v>
       </c>
       <c r="T20">
-        <v>1.113832865473454</v>
+        <v>1.124259083441005</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>25.60333300920604</v>
+        <v>24.25578916661625</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08341017883352639</v>
+        <v>0.0831977279455523</v>
       </c>
       <c r="C21">
-        <v>62.05998924512766</v>
+        <v>61.5425130298301</v>
       </c>
       <c r="D21">
-        <v>51.66898924512766</v>
+        <v>51.96251302983011</v>
       </c>
       <c r="E21">
-        <v>-17.891</v>
+        <v>-17.08</v>
       </c>
       <c r="F21">
-        <v>15.409</v>
+        <v>16.22</v>
       </c>
       <c r="G21">
         <v>25.8</v>
@@ -3131,28 +3131,28 @@
         <v>18.8</v>
       </c>
       <c r="M21">
-        <v>0.7750726999999999</v>
+        <v>0.8158659999999999</v>
       </c>
       <c r="N21">
-        <v>18.0249273</v>
+        <v>17.984134</v>
       </c>
       <c r="O21">
-        <v>5.046979644000001</v>
+        <v>5.035557520000001</v>
       </c>
       <c r="P21">
-        <v>12.977947656</v>
+        <v>12.94857648</v>
       </c>
       <c r="Q21">
-        <v>23.277947656</v>
+        <v>23.24857648</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09448041831299553</v>
+        <v>0.09494315993194036</v>
       </c>
       <c r="T21">
-        <v>1.124259083441005</v>
+        <v>1.134945956857745</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>24.25578916661625</v>
+        <v>23.04299970828544</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0831977279455523</v>
+        <v>0.08298527705757819</v>
       </c>
       <c r="C22">
-        <v>61.5425130298301</v>
+        <v>61.02839079727179</v>
       </c>
       <c r="D22">
-        <v>51.96251302983011</v>
+        <v>52.25939079727178</v>
       </c>
       <c r="E22">
-        <v>-17.08</v>
+        <v>-16.269</v>
       </c>
       <c r="F22">
-        <v>16.22</v>
+        <v>17.031</v>
       </c>
       <c r="G22">
         <v>25.8</v>
@@ -3213,28 +3213,28 @@
         <v>18.8</v>
       </c>
       <c r="M22">
-        <v>0.8158659999999999</v>
+        <v>0.8566592999999999</v>
       </c>
       <c r="N22">
-        <v>17.984134</v>
+        <v>17.9433407</v>
       </c>
       <c r="O22">
-        <v>5.035557520000001</v>
+        <v>5.024135396</v>
       </c>
       <c r="P22">
-        <v>12.94857648</v>
+        <v>12.919205304</v>
       </c>
       <c r="Q22">
-        <v>23.24857648</v>
+        <v>23.219205304</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09494315993194036</v>
+        <v>0.09541761652857997</v>
       </c>
       <c r="T22">
-        <v>1.134945956857745</v>
+        <v>1.14590338403187</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>23.04299970828544</v>
+        <v>21.94571400789089</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08298527705757819</v>
+        <v>0.08277282616960409</v>
       </c>
       <c r="C23">
-        <v>61.02839079727179</v>
+        <v>60.51768036477564</v>
       </c>
       <c r="D23">
-        <v>52.25939079727178</v>
+        <v>52.55968036477564</v>
       </c>
       <c r="E23">
-        <v>-16.269</v>
+        <v>-15.458</v>
       </c>
       <c r="F23">
-        <v>17.031</v>
+        <v>17.842</v>
       </c>
       <c r="G23">
         <v>25.8</v>
@@ -3295,28 +3295,28 @@
         <v>18.8</v>
       </c>
       <c r="M23">
-        <v>0.8566592999999999</v>
+        <v>0.8974525999999999</v>
       </c>
       <c r="N23">
-        <v>17.9433407</v>
+        <v>17.9025474</v>
       </c>
       <c r="O23">
-        <v>5.024135396</v>
+        <v>5.012713272</v>
       </c>
       <c r="P23">
-        <v>12.919205304</v>
+        <v>12.889834128</v>
       </c>
       <c r="Q23">
-        <v>23.219205304</v>
+        <v>23.189834128</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09541761652857997</v>
+        <v>0.0959042386789796</v>
       </c>
       <c r="T23">
-        <v>1.14590338403187</v>
+        <v>1.157141770877127</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>21.94571400789089</v>
+        <v>20.94818155298675</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08277282616960409</v>
+        <v>0.08256037528163</v>
       </c>
       <c r="C24">
-        <v>60.51768036477564</v>
+        <v>60.01044088624972</v>
       </c>
       <c r="D24">
-        <v>52.55968036477564</v>
+        <v>52.86344088624972</v>
       </c>
       <c r="E24">
-        <v>-15.458</v>
+        <v>-14.647</v>
       </c>
       <c r="F24">
-        <v>17.842</v>
+        <v>18.653</v>
       </c>
       <c r="G24">
         <v>25.8</v>
@@ -3377,28 +3377,28 @@
         <v>18.8</v>
       </c>
       <c r="M24">
-        <v>0.8974525999999999</v>
+        <v>0.9382458999999999</v>
       </c>
       <c r="N24">
-        <v>17.9025474</v>
+        <v>17.8617541</v>
       </c>
       <c r="O24">
-        <v>5.012713272</v>
+        <v>5.001291148000001</v>
       </c>
       <c r="P24">
-        <v>12.889834128</v>
+        <v>12.860462952</v>
       </c>
       <c r="Q24">
-        <v>23.189834128</v>
+        <v>23.160462952</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0959042386789796</v>
+        <v>0.09640350036575324</v>
       </c>
       <c r="T24">
-        <v>1.157141770877127</v>
+        <v>1.168672063874209</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>20.94818155298675</v>
+        <v>20.03739105068299</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08256037528163</v>
+        <v>0.08234792439365592</v>
       </c>
       <c r="C25">
-        <v>60.01044088624972</v>
+        <v>59.5067328910345</v>
       </c>
       <c r="D25">
-        <v>52.86344088624972</v>
+        <v>53.1707328910345</v>
       </c>
       <c r="E25">
-        <v>-14.647</v>
+        <v>-13.836</v>
       </c>
       <c r="F25">
-        <v>18.653</v>
+        <v>19.464</v>
       </c>
       <c r="G25">
         <v>25.8</v>
@@ -3459,28 +3459,28 @@
         <v>18.8</v>
       </c>
       <c r="M25">
-        <v>0.9382458999999999</v>
+        <v>0.9790391999999999</v>
       </c>
       <c r="N25">
-        <v>17.8617541</v>
+        <v>17.8209608</v>
       </c>
       <c r="O25">
-        <v>5.001291148000001</v>
+        <v>4.989869024000001</v>
       </c>
       <c r="P25">
-        <v>12.860462952</v>
+        <v>12.831091776</v>
       </c>
       <c r="Q25">
-        <v>23.160462952</v>
+        <v>23.131091776</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09640350036575324</v>
+        <v>0.09691590051796829</v>
       </c>
       <c r="T25">
-        <v>1.168672063874209</v>
+        <v>1.180505785634372</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.03739105068299</v>
+        <v>19.20249975690453</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0823479243936559</v>
+        <v>0.08213547350568182</v>
       </c>
       <c r="C26">
-        <v>59.50673289103453</v>
+        <v>59.00661832411323</v>
       </c>
       <c r="D26">
-        <v>53.17073289103453</v>
+        <v>53.48161832411322</v>
       </c>
       <c r="E26">
-        <v>-13.836</v>
+        <v>-13.025</v>
       </c>
       <c r="F26">
-        <v>19.464</v>
+        <v>20.275</v>
       </c>
       <c r="G26">
         <v>25.8</v>
@@ -3541,28 +3541,28 @@
         <v>18.8</v>
       </c>
       <c r="M26">
-        <v>0.9790391999999999</v>
+        <v>1.0198325</v>
       </c>
       <c r="N26">
-        <v>17.8209608</v>
+        <v>17.7801675</v>
       </c>
       <c r="O26">
-        <v>4.989869024000001</v>
+        <v>4.978446900000001</v>
       </c>
       <c r="P26">
-        <v>12.831091776</v>
+        <v>12.8017206</v>
       </c>
       <c r="Q26">
-        <v>23.131091776</v>
+        <v>23.1017206</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09691590051796829</v>
+        <v>0.0974419646742424</v>
       </c>
       <c r="T26">
-        <v>1.180505785634372</v>
+        <v>1.192655073308139</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.20249975690453</v>
+        <v>18.43439976662835</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08213547350568182</v>
+        <v>0.0819230226177077</v>
       </c>
       <c r="C27">
-        <v>59.00661832411323</v>
+        <v>58.51016058774098</v>
       </c>
       <c r="D27">
-        <v>53.48161832411322</v>
+        <v>53.79616058774098</v>
       </c>
       <c r="E27">
-        <v>-13.025</v>
+        <v>-12.214</v>
       </c>
       <c r="F27">
-        <v>20.275</v>
+        <v>21.086</v>
       </c>
       <c r="G27">
         <v>25.8</v>
@@ -3623,28 +3623,28 @@
         <v>18.8</v>
       </c>
       <c r="M27">
-        <v>1.0198325</v>
+        <v>1.0606258</v>
       </c>
       <c r="N27">
-        <v>17.7801675</v>
+        <v>17.7393742</v>
       </c>
       <c r="O27">
-        <v>4.978446900000001</v>
+        <v>4.967024776000001</v>
       </c>
       <c r="P27">
-        <v>12.8017206</v>
+        <v>12.772349424</v>
       </c>
       <c r="Q27">
-        <v>23.1017206</v>
+        <v>23.072349424</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0974419646742424</v>
+        <v>0.09798224678068609</v>
       </c>
       <c r="T27">
-        <v>1.192655073308139</v>
+        <v>1.205132720108224</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.43439976662835</v>
+        <v>17.72538439098879</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0819230226177077</v>
+        <v>0.08171057172973362</v>
       </c>
       <c r="C28">
-        <v>58.51016058774098</v>
+        <v>58.01742458455167</v>
       </c>
       <c r="D28">
-        <v>53.79616058774098</v>
+        <v>54.11442458455167</v>
       </c>
       <c r="E28">
-        <v>-12.214</v>
+        <v>-11.403</v>
       </c>
       <c r="F28">
-        <v>21.086</v>
+        <v>21.897</v>
       </c>
       <c r="G28">
         <v>25.8</v>
@@ -3705,28 +3705,28 @@
         <v>18.8</v>
       </c>
       <c r="M28">
-        <v>1.0606258</v>
+        <v>1.1014191</v>
       </c>
       <c r="N28">
-        <v>17.7393742</v>
+        <v>17.6985809</v>
       </c>
       <c r="O28">
-        <v>4.967024776000001</v>
+        <v>4.955602652</v>
       </c>
       <c r="P28">
-        <v>12.772349424</v>
+        <v>12.742978248</v>
       </c>
       <c r="Q28">
-        <v>23.072349424</v>
+        <v>23.042978248</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09798224678068609</v>
+        <v>0.09853733113662139</v>
       </c>
       <c r="T28">
-        <v>1.205132720108224</v>
+        <v>1.217952220245297</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>17.72538439098879</v>
+        <v>17.06888867280403</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08171057172973362</v>
+        <v>0.0814981208417595</v>
       </c>
       <c r="C29">
-        <v>58.01742458455167</v>
+        <v>57.52847676220433</v>
       </c>
       <c r="D29">
-        <v>54.11442458455167</v>
+        <v>54.43647676220433</v>
       </c>
       <c r="E29">
-        <v>-11.403</v>
+        <v>-10.592</v>
       </c>
       <c r="F29">
-        <v>21.897</v>
+        <v>22.708</v>
       </c>
       <c r="G29">
         <v>25.8</v>
@@ -3787,28 +3787,28 @@
         <v>18.8</v>
       </c>
       <c r="M29">
-        <v>1.1014191</v>
+        <v>1.1422124</v>
       </c>
       <c r="N29">
-        <v>17.6985809</v>
+        <v>17.6577876</v>
       </c>
       <c r="O29">
-        <v>4.955602652</v>
+        <v>4.944180528</v>
       </c>
       <c r="P29">
-        <v>12.742978248</v>
+        <v>12.713607072</v>
       </c>
       <c r="Q29">
-        <v>23.042978248</v>
+        <v>23.013607072</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09853733113662139</v>
+        <v>0.09910783450244377</v>
       </c>
       <c r="T29">
-        <v>1.217952220245297</v>
+        <v>1.231127817608401</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.06888867280403</v>
+        <v>16.45928550591816</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0814981208417595</v>
+        <v>0.08128566995378542</v>
       </c>
       <c r="C30">
-        <v>57.52847676220433</v>
+        <v>57.04338515963271</v>
       </c>
       <c r="D30">
-        <v>54.43647676220433</v>
+        <v>54.76238515963271</v>
       </c>
       <c r="E30">
-        <v>-10.592</v>
+        <v>-9.780999999999995</v>
       </c>
       <c r="F30">
-        <v>22.708</v>
+        <v>23.519</v>
       </c>
       <c r="G30">
         <v>25.8</v>
@@ -3869,28 +3869,28 @@
         <v>18.8</v>
       </c>
       <c r="M30">
-        <v>1.1422124</v>
+        <v>1.1830057</v>
       </c>
       <c r="N30">
-        <v>17.6577876</v>
+        <v>17.6169943</v>
       </c>
       <c r="O30">
-        <v>4.944180528</v>
+        <v>4.932758404000001</v>
       </c>
       <c r="P30">
-        <v>12.713607072</v>
+        <v>12.684235896</v>
       </c>
       <c r="Q30">
-        <v>23.013607072</v>
+        <v>22.984235896</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09910783450244377</v>
+        <v>0.09969440838561326</v>
       </c>
       <c r="T30">
-        <v>1.231127817608401</v>
+        <v>1.244674558559198</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.45928550591816</v>
+        <v>15.89172393674857</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0812856699537854</v>
+        <v>0.08107321906581132</v>
       </c>
       <c r="C31">
-        <v>57.04338515963274</v>
+        <v>56.56221945496701</v>
       </c>
       <c r="D31">
-        <v>54.76238515963274</v>
+        <v>55.092219454967</v>
       </c>
       <c r="E31">
-        <v>-9.780999999999999</v>
+        <v>-8.969999999999999</v>
       </c>
       <c r="F31">
-        <v>23.519</v>
+        <v>24.33</v>
       </c>
       <c r="G31">
         <v>25.8</v>
@@ -3951,28 +3951,28 @@
         <v>18.8</v>
       </c>
       <c r="M31">
-        <v>1.1830057</v>
+        <v>1.223799</v>
       </c>
       <c r="N31">
-        <v>17.6169943</v>
+        <v>17.576201</v>
       </c>
       <c r="O31">
-        <v>4.932758404000001</v>
+        <v>4.921336280000001</v>
       </c>
       <c r="P31">
-        <v>12.684235896</v>
+        <v>12.65486472</v>
       </c>
       <c r="Q31">
-        <v>22.984235896</v>
+        <v>22.95486472</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09969440838561326</v>
+        <v>0.1002977415225876</v>
       </c>
       <c r="T31">
-        <v>1.244674558559198</v>
+        <v>1.258608349251446</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.89172393674858</v>
+        <v>15.36199980552362</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08107321906581132</v>
+        <v>0.08086076817783722</v>
       </c>
       <c r="C32">
-        <v>56.56221945496701</v>
+        <v>56.08505101519706</v>
       </c>
       <c r="D32">
-        <v>55.092219454967</v>
+        <v>55.42605101519706</v>
       </c>
       <c r="E32">
-        <v>-8.969999999999999</v>
+        <v>-8.158999999999999</v>
       </c>
       <c r="F32">
-        <v>24.33</v>
+        <v>25.141</v>
       </c>
       <c r="G32">
         <v>25.8</v>
@@ -4033,28 +4033,28 @@
         <v>18.8</v>
       </c>
       <c r="M32">
-        <v>1.223799</v>
+        <v>1.2645923</v>
       </c>
       <c r="N32">
-        <v>17.576201</v>
+        <v>17.5354077</v>
       </c>
       <c r="O32">
-        <v>4.921336280000001</v>
+        <v>4.909914156</v>
       </c>
       <c r="P32">
-        <v>12.65486472</v>
+        <v>12.625493544</v>
       </c>
       <c r="Q32">
-        <v>22.95486472</v>
+        <v>22.925493544</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1002977415225876</v>
+        <v>0.1009185625765757</v>
       </c>
       <c r="T32">
-        <v>1.258608349251446</v>
+        <v>1.272946017934774</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.36199980552362</v>
+        <v>14.86645142470028</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08086076817783722</v>
+        <v>0.08064831728986312</v>
       </c>
       <c r="C33">
-        <v>56.08505101519706</v>
+        <v>55.61195294765282</v>
       </c>
       <c r="D33">
-        <v>55.42605101519706</v>
+        <v>55.76395294765283</v>
       </c>
       <c r="E33">
-        <v>-8.158999999999999</v>
+        <v>-7.347999999999999</v>
       </c>
       <c r="F33">
-        <v>25.141</v>
+        <v>25.952</v>
       </c>
       <c r="G33">
         <v>25.8</v>
@@ -4115,28 +4115,28 @@
         <v>18.8</v>
       </c>
       <c r="M33">
-        <v>1.2645923</v>
+        <v>1.3053856</v>
       </c>
       <c r="N33">
-        <v>17.5354077</v>
+        <v>17.4946144</v>
       </c>
       <c r="O33">
-        <v>4.909914156</v>
+        <v>4.898492032</v>
       </c>
       <c r="P33">
-        <v>12.625493544</v>
+        <v>12.596122368</v>
       </c>
       <c r="Q33">
-        <v>22.925493544</v>
+        <v>22.896122368</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1009185625765757</v>
+        <v>0.1015576430733281</v>
       </c>
       <c r="T33">
-        <v>1.272946017934774</v>
+        <v>1.287705382755846</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.86645142470028</v>
+        <v>14.40187481767839</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08064831728986312</v>
+        <v>0.08043586640188902</v>
       </c>
       <c r="C34">
-        <v>55.61195294765282</v>
+        <v>55.1430001533791</v>
       </c>
       <c r="D34">
-        <v>55.76395294765283</v>
+        <v>56.1060001533791</v>
       </c>
       <c r="E34">
-        <v>-7.347999999999999</v>
+        <v>-6.536999999999999</v>
       </c>
       <c r="F34">
-        <v>25.952</v>
+        <v>26.763</v>
       </c>
       <c r="G34">
         <v>25.8</v>
@@ -4197,28 +4197,28 @@
         <v>18.8</v>
       </c>
       <c r="M34">
-        <v>1.3053856</v>
+        <v>1.3461789</v>
       </c>
       <c r="N34">
-        <v>17.4946144</v>
+        <v>17.4538211</v>
       </c>
       <c r="O34">
-        <v>4.898492032</v>
+        <v>4.887069908000001</v>
       </c>
       <c r="P34">
-        <v>12.596122368</v>
+        <v>12.566751192</v>
       </c>
       <c r="Q34">
-        <v>22.896122368</v>
+        <v>22.866751192</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1015576430733281</v>
+        <v>0.1022158005998344</v>
       </c>
       <c r="T34">
-        <v>1.287705382755846</v>
+        <v>1.302905325631279</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.40187481767839</v>
+        <v>13.96545436865784</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08043586640188902</v>
+        <v>0.08022341551391493</v>
       </c>
       <c r="C35">
-        <v>55.1430001533791</v>
+        <v>54.67826938248687</v>
       </c>
       <c r="D35">
-        <v>56.1060001533791</v>
+        <v>56.45226938248687</v>
       </c>
       <c r="E35">
-        <v>-6.536999999999999</v>
+        <v>-5.725999999999996</v>
       </c>
       <c r="F35">
-        <v>26.763</v>
+        <v>27.574</v>
       </c>
       <c r="G35">
         <v>25.8</v>
@@ -4279,28 +4279,28 @@
         <v>18.8</v>
       </c>
       <c r="M35">
-        <v>1.3461789</v>
+        <v>1.3869722</v>
       </c>
       <c r="N35">
-        <v>17.4538211</v>
+        <v>17.4130278</v>
       </c>
       <c r="O35">
-        <v>4.887069908000001</v>
+        <v>4.875647784000001</v>
       </c>
       <c r="P35">
-        <v>12.566751192</v>
+        <v>12.537380016</v>
       </c>
       <c r="Q35">
-        <v>22.866751192</v>
+        <v>22.837380016</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1022158005998344</v>
+        <v>0.1028939022938105</v>
       </c>
       <c r="T35">
-        <v>1.302905325631279</v>
+        <v>1.318565872836271</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>13.96545436865784</v>
+        <v>13.55470571075614</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08022341551391493</v>
+        <v>0.08001096462594083</v>
       </c>
       <c r="C36">
-        <v>54.67826938248687</v>
+        <v>54.21783929156707</v>
       </c>
       <c r="D36">
-        <v>56.45226938248687</v>
+        <v>56.80283929156708</v>
       </c>
       <c r="E36">
-        <v>-5.725999999999996</v>
+        <v>-4.914999999999996</v>
       </c>
       <c r="F36">
-        <v>27.574</v>
+        <v>28.385</v>
       </c>
       <c r="G36">
         <v>25.8</v>
@@ -4361,28 +4361,28 @@
         <v>18.8</v>
       </c>
       <c r="M36">
-        <v>1.3869722</v>
+        <v>1.4277655</v>
       </c>
       <c r="N36">
-        <v>17.4130278</v>
+        <v>17.3722345</v>
       </c>
       <c r="O36">
-        <v>4.875647784000001</v>
+        <v>4.864225660000001</v>
       </c>
       <c r="P36">
-        <v>12.537380016</v>
+        <v>12.50800884</v>
       </c>
       <c r="Q36">
-        <v>22.837380016</v>
+        <v>22.80800884</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1028939022938105</v>
+        <v>0.1035928686552936</v>
       </c>
       <c r="T36">
-        <v>1.318565872836271</v>
+        <v>1.334708283032185</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.55470571075614</v>
+        <v>13.16742840473453</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08001096462594083</v>
+        <v>0.08018731373796674</v>
       </c>
       <c r="C37">
-        <v>54.21783929156707</v>
+        <v>53.11553621549812</v>
       </c>
       <c r="D37">
-        <v>56.80283929156708</v>
+        <v>56.51153621549812</v>
       </c>
       <c r="E37">
-        <v>-4.914999999999996</v>
+        <v>-4.103999999999996</v>
       </c>
       <c r="F37">
-        <v>28.385</v>
+        <v>29.196</v>
       </c>
       <c r="G37">
         <v>25.8</v>
@@ -4443,45 +4443,45 @@
         <v>18.8</v>
       </c>
       <c r="M37">
-        <v>1.4277655</v>
+        <v>1.5123528</v>
       </c>
       <c r="N37">
-        <v>17.3722345</v>
+        <v>17.2876472</v>
       </c>
       <c r="O37">
-        <v>4.864225660000001</v>
+        <v>4.840541216000001</v>
       </c>
       <c r="P37">
-        <v>12.50800884</v>
+        <v>12.447105984</v>
       </c>
       <c r="Q37">
-        <v>22.80800884</v>
+        <v>22.747105984</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1035928686552936</v>
+        <v>0.104313677715573</v>
       </c>
       <c r="T37">
-        <v>1.334708283032185</v>
+        <v>1.351355143546722</v>
       </c>
       <c r="U37">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V37">
         <v>0.28</v>
       </c>
       <c r="W37">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y37">
-        <v>13.16742840473453</v>
+        <v>12.43096187609135</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08018731373796675</v>
+        <v>0.07998566284999266</v>
       </c>
       <c r="C38">
-        <v>53.1155362154981</v>
+        <v>52.63788067948112</v>
       </c>
       <c r="D38">
-        <v>56.51153621549809</v>
+        <v>56.84488067948111</v>
       </c>
       <c r="E38">
-        <v>-4.103999999999999</v>
+        <v>-3.292999999999999</v>
       </c>
       <c r="F38">
-        <v>29.196</v>
+        <v>30.007</v>
       </c>
       <c r="G38">
         <v>25.8</v>
@@ -4525,28 +4525,28 @@
         <v>18.8</v>
       </c>
       <c r="M38">
-        <v>1.5123528</v>
+        <v>1.5543626</v>
       </c>
       <c r="N38">
-        <v>17.2876472</v>
+        <v>17.2456374</v>
       </c>
       <c r="O38">
-        <v>4.840541216000001</v>
+        <v>4.828778472000001</v>
       </c>
       <c r="P38">
-        <v>12.447105984</v>
+        <v>12.416858928</v>
       </c>
       <c r="Q38">
-        <v>22.747105984</v>
+        <v>22.716858928</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.104313677715573</v>
+        <v>0.1050573696031629</v>
       </c>
       <c r="T38">
-        <v>1.351355143546722</v>
+        <v>1.368530475823625</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>12.43096187609135</v>
+        <v>12.09498993349428</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07998566284999266</v>
+        <v>0.07978401196201856</v>
       </c>
       <c r="C39">
-        <v>52.63788067948112</v>
+        <v>52.16418107469667</v>
       </c>
       <c r="D39">
-        <v>56.84488067948111</v>
+        <v>57.18218107469666</v>
       </c>
       <c r="E39">
-        <v>-3.292999999999999</v>
+        <v>-2.481999999999999</v>
       </c>
       <c r="F39">
-        <v>30.007</v>
+        <v>30.818</v>
       </c>
       <c r="G39">
         <v>25.8</v>
@@ -4607,28 +4607,28 @@
         <v>18.8</v>
       </c>
       <c r="M39">
-        <v>1.5543626</v>
+        <v>1.5963724</v>
       </c>
       <c r="N39">
-        <v>17.2456374</v>
+        <v>17.2036276</v>
       </c>
       <c r="O39">
-        <v>4.828778472000001</v>
+        <v>4.817015728</v>
       </c>
       <c r="P39">
-        <v>12.416858928</v>
+        <v>12.386611872</v>
       </c>
       <c r="Q39">
-        <v>22.716858928</v>
+        <v>22.686611872</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1050573696031629</v>
+        <v>0.1058250515516428</v>
       </c>
       <c r="T39">
-        <v>1.368530475823625</v>
+        <v>1.386259851077202</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>12.09498993349428</v>
+        <v>11.77670072471812</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07978401196201856</v>
+        <v>0.07958236107404444</v>
       </c>
       <c r="C40">
-        <v>52.16418107469667</v>
+        <v>51.69450824140169</v>
       </c>
       <c r="D40">
-        <v>57.18218107469666</v>
+        <v>57.52350824140169</v>
       </c>
       <c r="E40">
-        <v>-2.481999999999999</v>
+        <v>-1.670999999999999</v>
       </c>
       <c r="F40">
-        <v>30.818</v>
+        <v>31.629</v>
       </c>
       <c r="G40">
         <v>25.8</v>
@@ -4689,28 +4689,28 @@
         <v>18.8</v>
       </c>
       <c r="M40">
-        <v>1.5963724</v>
+        <v>1.6383822</v>
       </c>
       <c r="N40">
-        <v>17.2036276</v>
+        <v>17.1616178</v>
       </c>
       <c r="O40">
-        <v>4.817015728</v>
+        <v>4.805252984000001</v>
       </c>
       <c r="P40">
-        <v>12.386611872</v>
+        <v>12.356364816</v>
       </c>
       <c r="Q40">
-        <v>22.686611872</v>
+        <v>22.656364816</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1058250515516428</v>
+        <v>0.1066179034000729</v>
       </c>
       <c r="T40">
-        <v>1.386259851077202</v>
+        <v>1.404570517322699</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.77670072471812</v>
+        <v>11.47473403946894</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07958236107404444</v>
+        <v>0.07938071018607036</v>
       </c>
       <c r="C41">
-        <v>51.69450824140169</v>
+        <v>51.22893472142518</v>
       </c>
       <c r="D41">
-        <v>57.52350824140169</v>
+        <v>57.86893472142518</v>
       </c>
       <c r="E41">
-        <v>-1.670999999999999</v>
+        <v>-0.8599999999999994</v>
       </c>
       <c r="F41">
-        <v>31.629</v>
+        <v>32.44</v>
       </c>
       <c r="G41">
         <v>25.8</v>
@@ -4771,28 +4771,28 @@
         <v>18.8</v>
       </c>
       <c r="M41">
-        <v>1.6383822</v>
+        <v>1.680392</v>
       </c>
       <c r="N41">
-        <v>17.1616178</v>
+        <v>17.119608</v>
       </c>
       <c r="O41">
-        <v>4.805252984000001</v>
+        <v>4.793490240000001</v>
       </c>
       <c r="P41">
-        <v>12.356364816</v>
+        <v>12.32611776</v>
       </c>
       <c r="Q41">
-        <v>22.656364816</v>
+        <v>22.62611776</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1066179034000729</v>
+        <v>0.1074371836434506</v>
       </c>
       <c r="T41">
-        <v>1.404570517322699</v>
+        <v>1.423491539109714</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.47473403946894</v>
+        <v>11.18786568848221</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07938071018607036</v>
+        <v>0.07917905929809627</v>
       </c>
       <c r="C42">
-        <v>51.22893472142518</v>
+        <v>50.76753480956653</v>
       </c>
       <c r="D42">
-        <v>57.86893472142518</v>
+        <v>58.21853480956653</v>
       </c>
       <c r="E42">
-        <v>-0.8599999999999994</v>
+        <v>-0.04899999999999949</v>
       </c>
       <c r="F42">
-        <v>32.44</v>
+        <v>33.251</v>
       </c>
       <c r="G42">
         <v>25.8</v>
@@ -4853,28 +4853,28 @@
         <v>18.8</v>
       </c>
       <c r="M42">
-        <v>1.680392</v>
+        <v>1.7224018</v>
       </c>
       <c r="N42">
-        <v>17.119608</v>
+        <v>17.0775982</v>
       </c>
       <c r="O42">
-        <v>4.793490240000001</v>
+        <v>4.781727496</v>
       </c>
       <c r="P42">
-        <v>12.32611776</v>
+        <v>12.295870704</v>
       </c>
       <c r="Q42">
-        <v>22.62611776</v>
+        <v>22.595870704</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1074371836434506</v>
+        <v>0.1082842360984683</v>
       </c>
       <c r="T42">
-        <v>1.423491539109714</v>
+        <v>1.44305395146578</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.18786568848221</v>
+        <v>10.9149909155924</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07917905929809627</v>
+        <v>0.07897740841012217</v>
       </c>
       <c r="C43">
-        <v>50.76753480956653</v>
+        <v>50.31038460686771</v>
       </c>
       <c r="D43">
-        <v>58.21853480956653</v>
+        <v>58.57238460686771</v>
       </c>
       <c r="E43">
-        <v>-0.04899999999999949</v>
+        <v>0.7620000000000005</v>
       </c>
       <c r="F43">
-        <v>33.251</v>
+        <v>34.062</v>
       </c>
       <c r="G43">
         <v>25.8</v>
@@ -4935,28 +4935,28 @@
         <v>18.8</v>
       </c>
       <c r="M43">
-        <v>1.7224018</v>
+        <v>1.7644116</v>
       </c>
       <c r="N43">
-        <v>17.0775982</v>
+        <v>17.0355884</v>
       </c>
       <c r="O43">
-        <v>4.781727496</v>
+        <v>4.769964752000001</v>
       </c>
       <c r="P43">
-        <v>12.295870704</v>
+        <v>12.265623648</v>
       </c>
       <c r="Q43">
-        <v>22.595870704</v>
+        <v>22.565623648</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1082842360984683</v>
+        <v>0.1091604972588313</v>
       </c>
       <c r="T43">
-        <v>1.44305395146578</v>
+        <v>1.463290929765158</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.9149909155924</v>
+        <v>10.65511017950687</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07897740841012219</v>
+        <v>0.07877575752214809</v>
       </c>
       <c r="C44">
-        <v>50.31038460686769</v>
+        <v>49.85756207584023</v>
       </c>
       <c r="D44">
-        <v>58.57238460686768</v>
+        <v>58.93056207584022</v>
       </c>
       <c r="E44">
-        <v>0.7620000000000005</v>
+        <v>1.573</v>
       </c>
       <c r="F44">
-        <v>34.062</v>
+        <v>34.873</v>
       </c>
       <c r="G44">
         <v>25.8</v>
@@ -5017,28 +5017,28 @@
         <v>18.8</v>
       </c>
       <c r="M44">
-        <v>1.7644116</v>
+        <v>1.8064214</v>
       </c>
       <c r="N44">
-        <v>17.0355884</v>
+        <v>16.9935786</v>
       </c>
       <c r="O44">
-        <v>4.769964752000001</v>
+        <v>4.758202008</v>
       </c>
       <c r="P44">
-        <v>12.265623648</v>
+        <v>12.235376592</v>
       </c>
       <c r="Q44">
-        <v>22.565623648</v>
+        <v>22.535376592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1091604972588313</v>
+        <v>0.1100675044248212</v>
       </c>
       <c r="T44">
-        <v>1.463290929765158</v>
+        <v>1.484237977478549</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.65511017950687</v>
+        <v>10.40731691951834</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07877575752214809</v>
+        <v>0.078574106634174</v>
       </c>
       <c r="C45">
-        <v>49.85756207584023</v>
+        <v>49.40914709773109</v>
       </c>
       <c r="D45">
-        <v>58.93056207584022</v>
+        <v>59.29314709773109</v>
       </c>
       <c r="E45">
-        <v>1.573</v>
+        <v>2.384</v>
       </c>
       <c r="F45">
-        <v>34.873</v>
+        <v>35.684</v>
       </c>
       <c r="G45">
         <v>25.8</v>
@@ -5099,28 +5099,28 @@
         <v>18.8</v>
       </c>
       <c r="M45">
-        <v>1.8064214</v>
+        <v>1.8484312</v>
       </c>
       <c r="N45">
-        <v>16.9935786</v>
+        <v>16.9515688</v>
       </c>
       <c r="O45">
-        <v>4.758202008</v>
+        <v>4.746439264</v>
       </c>
       <c r="P45">
-        <v>12.235376592</v>
+        <v>12.205129536</v>
       </c>
       <c r="Q45">
-        <v>22.535376592</v>
+        <v>22.505129536</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1100675044248212</v>
+        <v>0.1110069047038821</v>
       </c>
       <c r="T45">
-        <v>1.484237977478549</v>
+        <v>1.505933134038848</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.40731691951834</v>
+        <v>10.17078698952928</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.078574106634174</v>
+        <v>0.07837245574619989</v>
       </c>
       <c r="C46">
-        <v>49.40914709773109</v>
+        <v>48.96522153191562</v>
       </c>
       <c r="D46">
-        <v>59.29314709773109</v>
+        <v>59.66022153191562</v>
       </c>
       <c r="E46">
-        <v>2.384</v>
+        <v>3.195</v>
       </c>
       <c r="F46">
-        <v>35.684</v>
+        <v>36.495</v>
       </c>
       <c r="G46">
         <v>25.8</v>
@@ -5181,28 +5181,28 @@
         <v>18.8</v>
       </c>
       <c r="M46">
-        <v>1.8484312</v>
+        <v>1.890441</v>
       </c>
       <c r="N46">
-        <v>16.9515688</v>
+        <v>16.909559</v>
       </c>
       <c r="O46">
-        <v>4.746439264</v>
+        <v>4.734676520000001</v>
       </c>
       <c r="P46">
-        <v>12.205129536</v>
+        <v>12.17488248</v>
       </c>
       <c r="Q46">
-        <v>22.505129536</v>
+        <v>22.47488248</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1110069047038821</v>
+        <v>0.1119804649930907</v>
       </c>
       <c r="T46">
-        <v>1.505933134038848</v>
+        <v>1.528417205383157</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.17078698952928</v>
+        <v>9.944769500873079</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07837245574619989</v>
+        <v>0.07873384485822579</v>
       </c>
       <c r="C47">
-        <v>48.96522153191562</v>
+        <v>47.49955899325663</v>
       </c>
       <c r="D47">
-        <v>59.66022153191562</v>
+        <v>59.00555899325662</v>
       </c>
       <c r="E47">
-        <v>3.195</v>
+        <v>4.006</v>
       </c>
       <c r="F47">
-        <v>36.495</v>
+        <v>37.306</v>
       </c>
       <c r="G47">
         <v>25.8</v>
@@ -5263,45 +5263,45 @@
         <v>18.8</v>
       </c>
       <c r="M47">
-        <v>1.890441</v>
+        <v>1.995871</v>
       </c>
       <c r="N47">
-        <v>16.909559</v>
+        <v>16.804129</v>
       </c>
       <c r="O47">
-        <v>4.734676520000001</v>
+        <v>4.705156120000001</v>
       </c>
       <c r="P47">
-        <v>12.17488248</v>
+        <v>12.09897288</v>
       </c>
       <c r="Q47">
-        <v>22.47488248</v>
+        <v>22.39897288</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1119804649930907</v>
+        <v>0.1129900830707885</v>
       </c>
       <c r="T47">
-        <v>1.528417205383157</v>
+        <v>1.551734020110589</v>
       </c>
       <c r="U47">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V47">
         <v>0.28</v>
       </c>
       <c r="W47">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>9.944769500873079</v>
+        <v>9.419446447190225</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07873384485822579</v>
+        <v>0.0785444339702517</v>
       </c>
       <c r="C48">
-        <v>47.49955899325663</v>
+        <v>47.0298779280861</v>
       </c>
       <c r="D48">
-        <v>59.00555899325662</v>
+        <v>59.3468779280861</v>
       </c>
       <c r="E48">
-        <v>4.006</v>
+        <v>4.817</v>
       </c>
       <c r="F48">
-        <v>37.306</v>
+        <v>38.117</v>
       </c>
       <c r="G48">
         <v>25.8</v>
@@ -5345,28 +5345,28 @@
         <v>18.8</v>
       </c>
       <c r="M48">
-        <v>1.995871</v>
+        <v>2.0392595</v>
       </c>
       <c r="N48">
-        <v>16.804129</v>
+        <v>16.7607405</v>
       </c>
       <c r="O48">
-        <v>4.705156120000001</v>
+        <v>4.69300734</v>
       </c>
       <c r="P48">
-        <v>12.09897288</v>
+        <v>12.06773316</v>
       </c>
       <c r="Q48">
-        <v>22.39897288</v>
+        <v>22.36773316</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1129900830707885</v>
+        <v>0.1140377999438711</v>
       </c>
       <c r="T48">
-        <v>1.551734020110589</v>
+        <v>1.575930714639056</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.419446447190225</v>
+        <v>9.219032692994688</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0785444339702517</v>
+        <v>0.0783550230822776</v>
       </c>
       <c r="C49">
-        <v>47.0298779280861</v>
+        <v>46.56416857089842</v>
       </c>
       <c r="D49">
-        <v>59.3468779280861</v>
+        <v>59.69216857089842</v>
       </c>
       <c r="E49">
-        <v>4.817</v>
+        <v>5.628</v>
       </c>
       <c r="F49">
-        <v>38.117</v>
+        <v>38.928</v>
       </c>
       <c r="G49">
         <v>25.8</v>
@@ -5427,28 +5427,28 @@
         <v>18.8</v>
       </c>
       <c r="M49">
-        <v>2.0392595</v>
+        <v>2.082648</v>
       </c>
       <c r="N49">
-        <v>16.7607405</v>
+        <v>16.717352</v>
       </c>
       <c r="O49">
-        <v>4.69300734</v>
+        <v>4.680858560000001</v>
       </c>
       <c r="P49">
-        <v>12.06773316</v>
+        <v>12.03649344</v>
       </c>
       <c r="Q49">
-        <v>22.36773316</v>
+        <v>22.33649344</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1140377999438711</v>
+        <v>0.1151258136197646</v>
       </c>
       <c r="T49">
-        <v>1.575930714639056</v>
+        <v>1.601058051264772</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>9.219032692994688</v>
+        <v>9.026969511890632</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0783550230822776</v>
+        <v>0.0781656121943035</v>
       </c>
       <c r="C50">
-        <v>46.56416857089842</v>
+        <v>46.10250065169569</v>
       </c>
       <c r="D50">
-        <v>59.69216857089842</v>
+        <v>60.04150065169568</v>
       </c>
       <c r="E50">
-        <v>5.628</v>
+        <v>6.439</v>
       </c>
       <c r="F50">
-        <v>38.928</v>
+        <v>39.739</v>
       </c>
       <c r="G50">
         <v>25.8</v>
@@ -5509,28 +5509,28 @@
         <v>18.8</v>
       </c>
       <c r="M50">
-        <v>2.082648</v>
+        <v>2.1260365</v>
       </c>
       <c r="N50">
-        <v>16.717352</v>
+        <v>16.6739635</v>
       </c>
       <c r="O50">
-        <v>4.680858560000001</v>
+        <v>4.66870978</v>
       </c>
       <c r="P50">
-        <v>12.03649344</v>
+        <v>12.00525372</v>
       </c>
       <c r="Q50">
-        <v>22.33649344</v>
+        <v>22.30525372</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1151258136197646</v>
+        <v>0.1162564944986343</v>
       </c>
       <c r="T50">
-        <v>1.601058051264772</v>
+        <v>1.627170773640515</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.026969511890632</v>
+        <v>8.842745644301027</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0781656121943035</v>
+        <v>0.07797620130632942</v>
       </c>
       <c r="C51">
-        <v>46.10250065169569</v>
+        <v>45.64494554239188</v>
       </c>
       <c r="D51">
-        <v>60.04150065169568</v>
+        <v>60.39494554239187</v>
       </c>
       <c r="E51">
-        <v>6.439</v>
+        <v>7.25</v>
       </c>
       <c r="F51">
-        <v>39.739</v>
+        <v>40.55</v>
       </c>
       <c r="G51">
         <v>25.8</v>
@@ -5591,28 +5591,28 @@
         <v>18.8</v>
       </c>
       <c r="M51">
-        <v>2.1260365</v>
+        <v>2.169425</v>
       </c>
       <c r="N51">
-        <v>16.6739635</v>
+        <v>16.630575</v>
       </c>
       <c r="O51">
-        <v>4.66870978</v>
+        <v>4.656561000000001</v>
       </c>
       <c r="P51">
-        <v>12.00525372</v>
+        <v>11.974014</v>
       </c>
       <c r="Q51">
-        <v>22.30525372</v>
+        <v>22.274014</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1162564944986343</v>
+        <v>0.1174324026126588</v>
       </c>
       <c r="T51">
-        <v>1.627170773640515</v>
+        <v>1.654328004911289</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.842745644301027</v>
+        <v>8.665890731415008</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07797620130632942</v>
+        <v>0.0777867904183553</v>
       </c>
       <c r="C52">
-        <v>45.64494554239188</v>
+        <v>45.1915763054261</v>
       </c>
       <c r="D52">
-        <v>60.39494554239187</v>
+        <v>60.7525763054261</v>
       </c>
       <c r="E52">
-        <v>7.25</v>
+        <v>8.061</v>
       </c>
       <c r="F52">
-        <v>40.55</v>
+        <v>41.361</v>
       </c>
       <c r="G52">
         <v>25.8</v>
@@ -5673,28 +5673,28 @@
         <v>18.8</v>
       </c>
       <c r="M52">
-        <v>2.169425</v>
+        <v>2.2128135</v>
       </c>
       <c r="N52">
-        <v>16.630575</v>
+        <v>16.5871865</v>
       </c>
       <c r="O52">
-        <v>4.656561000000001</v>
+        <v>4.64441222</v>
       </c>
       <c r="P52">
-        <v>11.974014</v>
+        <v>11.94277428</v>
       </c>
       <c r="Q52">
-        <v>22.274014</v>
+        <v>22.24277428</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1174324026126588</v>
+        <v>0.1186563069762353</v>
       </c>
       <c r="T52">
-        <v>1.654328004911289</v>
+        <v>1.682593694601278</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.665890731415008</v>
+        <v>8.495971305308831</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0777867904183553</v>
+        <v>0.07759737953038122</v>
       </c>
       <c r="C53">
-        <v>45.1915763054261</v>
+        <v>44.74246774411304</v>
       </c>
       <c r="D53">
-        <v>60.7525763054261</v>
+        <v>61.11446774411304</v>
       </c>
       <c r="E53">
-        <v>8.061</v>
+        <v>8.872</v>
       </c>
       <c r="F53">
-        <v>41.361</v>
+        <v>42.172</v>
       </c>
       <c r="G53">
         <v>25.8</v>
@@ -5755,28 +5755,28 @@
         <v>18.8</v>
       </c>
       <c r="M53">
-        <v>2.2128135</v>
+        <v>2.256202</v>
       </c>
       <c r="N53">
-        <v>16.5871865</v>
+        <v>16.543798</v>
       </c>
       <c r="O53">
-        <v>4.64441222</v>
+        <v>4.632263440000001</v>
       </c>
       <c r="P53">
-        <v>11.94277428</v>
+        <v>11.91153456</v>
       </c>
       <c r="Q53">
-        <v>22.24277428</v>
+        <v>22.21153456</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1186563069762353</v>
+        <v>0.1199312073549609</v>
       </c>
       <c r="T53">
-        <v>1.682593694601278</v>
+        <v>1.712037121361683</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.495971305308831</v>
+        <v>8.332587241745202</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07759737953038122</v>
+        <v>0.07740796864240712</v>
       </c>
       <c r="C54">
-        <v>44.74246774411304</v>
+        <v>44.29769645480425</v>
       </c>
       <c r="D54">
-        <v>61.11446774411304</v>
+        <v>61.48069645480425</v>
       </c>
       <c r="E54">
-        <v>8.872</v>
+        <v>9.683</v>
       </c>
       <c r="F54">
-        <v>42.172</v>
+        <v>42.983</v>
       </c>
       <c r="G54">
         <v>25.8</v>
@@ -5837,28 +5837,28 @@
         <v>18.8</v>
       </c>
       <c r="M54">
-        <v>2.256202</v>
+        <v>2.2995905</v>
       </c>
       <c r="N54">
-        <v>16.543798</v>
+        <v>16.5004095</v>
       </c>
       <c r="O54">
-        <v>4.632263440000001</v>
+        <v>4.62011466</v>
       </c>
       <c r="P54">
-        <v>11.91153456</v>
+        <v>11.88029484</v>
       </c>
       <c r="Q54">
-        <v>22.21153456</v>
+        <v>22.18029484</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1199312073549609</v>
+        <v>0.1212603588136322</v>
       </c>
       <c r="T54">
-        <v>1.712037121361683</v>
+        <v>1.742733459899127</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.332587241745202</v>
+        <v>8.17536861454246</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07740796864240712</v>
+        <v>0.07721855775443304</v>
       </c>
       <c r="C55">
-        <v>44.29769645480425</v>
+        <v>43.85734088093569</v>
       </c>
       <c r="D55">
-        <v>61.48069645480425</v>
+        <v>61.85134088093569</v>
       </c>
       <c r="E55">
-        <v>9.683</v>
+        <v>10.494</v>
       </c>
       <c r="F55">
-        <v>42.983</v>
+        <v>43.794</v>
       </c>
       <c r="G55">
         <v>25.8</v>
@@ -5919,28 +5919,28 @@
         <v>18.8</v>
       </c>
       <c r="M55">
-        <v>2.2995905</v>
+        <v>2.342979</v>
       </c>
       <c r="N55">
-        <v>16.5004095</v>
+        <v>16.457021</v>
       </c>
       <c r="O55">
-        <v>4.62011466</v>
+        <v>4.607965880000001</v>
       </c>
       <c r="P55">
-        <v>11.88029484</v>
+        <v>11.84905512</v>
       </c>
       <c r="Q55">
-        <v>22.18029484</v>
+        <v>22.14905512</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1212603588136322</v>
+        <v>0.1226472994661588</v>
       </c>
       <c r="T55">
-        <v>1.742733459899127</v>
+        <v>1.774764421851242</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.17536861454246</v>
+        <v>8.023972899458339</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07721855775443304</v>
+        <v>0.07702914686645894</v>
       </c>
       <c r="C56">
-        <v>43.85734088093569</v>
+        <v>43.42148136904262</v>
       </c>
       <c r="D56">
-        <v>61.85134088093569</v>
+        <v>62.22648136904263</v>
       </c>
       <c r="E56">
-        <v>10.494</v>
+        <v>11.30500000000001</v>
       </c>
       <c r="F56">
-        <v>43.794</v>
+        <v>44.605</v>
       </c>
       <c r="G56">
         <v>25.8</v>
@@ -6001,28 +6001,28 @@
         <v>18.8</v>
       </c>
       <c r="M56">
-        <v>2.342979</v>
+        <v>2.3863675</v>
       </c>
       <c r="N56">
-        <v>16.457021</v>
+        <v>16.4136325</v>
       </c>
       <c r="O56">
-        <v>4.607965880000001</v>
+        <v>4.595817100000001</v>
       </c>
       <c r="P56">
-        <v>11.84905512</v>
+        <v>11.8178154</v>
       </c>
       <c r="Q56">
-        <v>22.14905512</v>
+        <v>22.1178154</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1226472994661588</v>
+        <v>0.1240958819254643</v>
       </c>
       <c r="T56">
-        <v>1.774764421851242</v>
+        <v>1.80821898211234</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.023972899458339</v>
+        <v>7.878082483104552</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07702914686645894</v>
+        <v>0.07683973597848483</v>
       </c>
       <c r="C57">
-        <v>43.42148136904262</v>
+        <v>42.99020022682493</v>
       </c>
       <c r="D57">
-        <v>62.22648136904263</v>
+        <v>62.60620022682494</v>
       </c>
       <c r="E57">
-        <v>11.30500000000001</v>
+        <v>12.11600000000001</v>
       </c>
       <c r="F57">
-        <v>44.605</v>
+        <v>45.416</v>
       </c>
       <c r="G57">
         <v>25.8</v>
@@ -6083,28 +6083,28 @@
         <v>18.8</v>
       </c>
       <c r="M57">
-        <v>2.3863675</v>
+        <v>2.429756</v>
       </c>
       <c r="N57">
-        <v>16.4136325</v>
+        <v>16.370244</v>
       </c>
       <c r="O57">
-        <v>4.595817100000001</v>
+        <v>4.58366832</v>
       </c>
       <c r="P57">
-        <v>11.8178154</v>
+        <v>11.78657568</v>
       </c>
       <c r="Q57">
-        <v>22.1178154</v>
+        <v>22.08657568</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1240958819254643</v>
+        <v>0.125610309042011</v>
       </c>
       <c r="T57">
-        <v>1.80821898211234</v>
+        <v>1.843194204203487</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.878082483104552</v>
+        <v>7.737402438763398</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07683973597848483</v>
+        <v>0.07697864509051072</v>
       </c>
       <c r="C58">
-        <v>42.99020022682493</v>
+        <v>41.90027304267124</v>
       </c>
       <c r="D58">
-        <v>62.60620022682494</v>
+        <v>62.32727304267125</v>
       </c>
       <c r="E58">
-        <v>12.11600000000001</v>
+        <v>12.92700000000001</v>
       </c>
       <c r="F58">
-        <v>45.416</v>
+        <v>46.227</v>
       </c>
       <c r="G58">
         <v>25.8</v>
@@ -6165,45 +6165,45 @@
         <v>18.8</v>
       </c>
       <c r="M58">
-        <v>2.429756</v>
+        <v>2.5101261</v>
       </c>
       <c r="N58">
-        <v>16.370244</v>
+        <v>16.2898739</v>
       </c>
       <c r="O58">
-        <v>4.58366832</v>
+        <v>4.561164692</v>
       </c>
       <c r="P58">
-        <v>11.78657568</v>
+        <v>11.728709208</v>
       </c>
       <c r="Q58">
-        <v>22.08657568</v>
+        <v>22.028709208</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.125610309042011</v>
+        <v>0.1271951746290947</v>
       </c>
       <c r="T58">
-        <v>1.843194204203487</v>
+        <v>1.879796180810502</v>
       </c>
       <c r="U58">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V58">
         <v>0.28</v>
       </c>
       <c r="W58">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y58">
-        <v>7.737402438763398</v>
+        <v>7.489663567101269</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07697864509051072</v>
+        <v>0.07679499420253665</v>
       </c>
       <c r="C59">
-        <v>41.90027304267124</v>
+        <v>41.45857329046262</v>
       </c>
       <c r="D59">
-        <v>62.32727304267125</v>
+        <v>62.69657329046262</v>
       </c>
       <c r="E59">
-        <v>12.92700000000001</v>
+        <v>13.73800000000001</v>
       </c>
       <c r="F59">
-        <v>46.227</v>
+        <v>47.038</v>
       </c>
       <c r="G59">
         <v>25.8</v>
@@ -6247,28 +6247,28 @@
         <v>18.8</v>
       </c>
       <c r="M59">
-        <v>2.5101261</v>
+        <v>2.5541634</v>
       </c>
       <c r="N59">
-        <v>16.2898739</v>
+        <v>16.2458366</v>
       </c>
       <c r="O59">
-        <v>4.561164692</v>
+        <v>4.548834248</v>
       </c>
       <c r="P59">
-        <v>11.728709208</v>
+        <v>11.697002352</v>
       </c>
       <c r="Q59">
-        <v>22.028709208</v>
+        <v>21.997002352</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1271951746290947</v>
+        <v>0.1288555100060396</v>
       </c>
       <c r="T59">
-        <v>1.879796180810502</v>
+        <v>1.918141108684518</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.489663567101269</v>
+        <v>7.360531436634007</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07679499420253665</v>
+        <v>0.07661134331456255</v>
       </c>
       <c r="C60">
-        <v>41.45857329046262</v>
+        <v>41.02127596353902</v>
       </c>
       <c r="D60">
-        <v>62.69657329046262</v>
+        <v>63.07027596353901</v>
       </c>
       <c r="E60">
-        <v>13.738</v>
+        <v>14.549</v>
       </c>
       <c r="F60">
-        <v>47.038</v>
+        <v>47.849</v>
       </c>
       <c r="G60">
         <v>25.8</v>
@@ -6329,28 +6329,28 @@
         <v>18.8</v>
       </c>
       <c r="M60">
-        <v>2.5541634</v>
+        <v>2.5982007</v>
       </c>
       <c r="N60">
-        <v>16.2458366</v>
+        <v>16.2017993</v>
       </c>
       <c r="O60">
-        <v>4.548834248</v>
+        <v>4.536503804000001</v>
       </c>
       <c r="P60">
-        <v>11.697002352</v>
+        <v>11.665295496</v>
       </c>
       <c r="Q60">
-        <v>21.997002352</v>
+        <v>21.965295496</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1288555100060396</v>
+        <v>0.1305968373525916</v>
       </c>
       <c r="T60">
-        <v>1.918141108684518</v>
+        <v>1.958356520845071</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.360531436634008</v>
+        <v>7.235776666521566</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07661134331456255</v>
+        <v>0.07642769242658845</v>
       </c>
       <c r="C61">
-        <v>41.02127596353902</v>
+        <v>40.58846025585026</v>
       </c>
       <c r="D61">
-        <v>63.07027596353901</v>
+        <v>63.44846025585026</v>
       </c>
       <c r="E61">
-        <v>14.549</v>
+        <v>15.36</v>
       </c>
       <c r="F61">
-        <v>47.849</v>
+        <v>48.66</v>
       </c>
       <c r="G61">
         <v>25.8</v>
@@ -6411,28 +6411,28 @@
         <v>18.8</v>
       </c>
       <c r="M61">
-        <v>2.5982007</v>
+        <v>2.642238</v>
       </c>
       <c r="N61">
-        <v>16.2017993</v>
+        <v>16.157762</v>
       </c>
       <c r="O61">
-        <v>4.536503804000001</v>
+        <v>4.524173360000001</v>
       </c>
       <c r="P61">
-        <v>11.665295496</v>
+        <v>11.63358864</v>
       </c>
       <c r="Q61">
-        <v>21.965295496</v>
+        <v>21.93358864</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1305968373525916</v>
+        <v>0.1324252310664711</v>
       </c>
       <c r="T61">
-        <v>1.958356520845071</v>
+        <v>2.000582703613652</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.235776666521566</v>
+        <v>7.115180388746208</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07642769242658845</v>
+        <v>0.07624404153861436</v>
       </c>
       <c r="C62">
-        <v>40.58846025585026</v>
+        <v>40.16020727226712</v>
       </c>
       <c r="D62">
-        <v>63.44846025585026</v>
+        <v>63.83120727226712</v>
       </c>
       <c r="E62">
-        <v>15.36</v>
+        <v>16.171</v>
       </c>
       <c r="F62">
-        <v>48.66</v>
+        <v>49.471</v>
       </c>
       <c r="G62">
         <v>25.8</v>
@@ -6493,28 +6493,28 @@
         <v>18.8</v>
       </c>
       <c r="M62">
-        <v>2.642238</v>
+        <v>2.6862753</v>
       </c>
       <c r="N62">
-        <v>16.157762</v>
+        <v>16.1137247</v>
       </c>
       <c r="O62">
-        <v>4.524173360000001</v>
+        <v>4.511842916000001</v>
       </c>
       <c r="P62">
-        <v>11.63358864</v>
+        <v>11.601881784</v>
       </c>
       <c r="Q62">
-        <v>21.93358864</v>
+        <v>21.901881784</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1324252310664711</v>
+        <v>0.1343473885605496</v>
       </c>
       <c r="T62">
-        <v>2.000582703613652</v>
+        <v>2.044974331652416</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.115180388746208</v>
+        <v>6.998538087291353</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07624404153861436</v>
+        <v>0.07606039065064027</v>
       </c>
       <c r="C63">
-        <v>40.16020727226712</v>
+        <v>39.73660008656849</v>
       </c>
       <c r="D63">
-        <v>63.83120727226712</v>
+        <v>64.21860008656849</v>
       </c>
       <c r="E63">
-        <v>16.171</v>
+        <v>16.982</v>
       </c>
       <c r="F63">
-        <v>49.471</v>
+        <v>50.282</v>
       </c>
       <c r="G63">
         <v>25.8</v>
@@ -6575,28 +6575,28 @@
         <v>18.8</v>
       </c>
       <c r="M63">
-        <v>2.6862753</v>
+        <v>2.7303126</v>
       </c>
       <c r="N63">
-        <v>16.1137247</v>
+        <v>16.0696874</v>
       </c>
       <c r="O63">
-        <v>4.511842916000001</v>
+        <v>4.499512472</v>
       </c>
       <c r="P63">
-        <v>11.601881784</v>
+        <v>11.570174928</v>
       </c>
       <c r="Q63">
-        <v>21.901881784</v>
+        <v>21.870174928</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1343473885605496</v>
+        <v>0.136370712238527</v>
       </c>
       <c r="T63">
-        <v>2.044974331652416</v>
+        <v>2.091702361166905</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.998538087291353</v>
+        <v>6.885658440722136</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07606039065064027</v>
+        <v>0.07587673976266615</v>
       </c>
       <c r="C64">
-        <v>39.73660008656849</v>
+        <v>39.31772380155279</v>
       </c>
       <c r="D64">
-        <v>64.21860008656849</v>
+        <v>64.61072380155279</v>
       </c>
       <c r="E64">
-        <v>16.982</v>
+        <v>17.793</v>
       </c>
       <c r="F64">
-        <v>50.282</v>
+        <v>51.093</v>
       </c>
       <c r="G64">
         <v>25.8</v>
@@ -6657,28 +6657,28 @@
         <v>18.8</v>
       </c>
       <c r="M64">
-        <v>2.7303126</v>
+        <v>2.7743499</v>
       </c>
       <c r="N64">
-        <v>16.0696874</v>
+        <v>16.0256501</v>
       </c>
       <c r="O64">
-        <v>4.499512472</v>
+        <v>4.487182028</v>
       </c>
       <c r="P64">
-        <v>11.570174928</v>
+        <v>11.538468072</v>
       </c>
       <c r="Q64">
-        <v>21.870174928</v>
+        <v>21.838468072</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.136370712238527</v>
+        <v>0.1385034047639626</v>
       </c>
       <c r="T64">
-        <v>2.091702361166905</v>
+        <v>2.14095623011461</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.885658440722136</v>
+        <v>6.776362274996388</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07587673976266615</v>
+        <v>0.07569308887469207</v>
       </c>
       <c r="C65">
-        <v>39.31772380155279</v>
+        <v>38.90366561136518</v>
       </c>
       <c r="D65">
-        <v>64.61072380155279</v>
+        <v>65.00766561136518</v>
       </c>
       <c r="E65">
-        <v>17.793</v>
+        <v>18.604</v>
       </c>
       <c r="F65">
-        <v>51.093</v>
+        <v>51.904</v>
       </c>
       <c r="G65">
         <v>25.8</v>
@@ -6739,28 +6739,28 @@
         <v>18.8</v>
       </c>
       <c r="M65">
-        <v>2.7743499</v>
+        <v>2.8183872</v>
       </c>
       <c r="N65">
-        <v>16.0256501</v>
+        <v>15.9816128</v>
       </c>
       <c r="O65">
-        <v>4.487182028</v>
+        <v>4.474851584</v>
       </c>
       <c r="P65">
-        <v>11.538468072</v>
+        <v>11.506761216</v>
       </c>
       <c r="Q65">
-        <v>21.838468072</v>
+        <v>21.806761216</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1385034047639626</v>
+        <v>0.140754580207478</v>
       </c>
       <c r="T65">
-        <v>2.14095623011461</v>
+        <v>2.192946425114965</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.776362274996388</v>
+        <v>6.67048161444957</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07569308887469207</v>
+        <v>0.07550943798671797</v>
       </c>
       <c r="C66">
-        <v>38.90366561136518</v>
+        <v>38.49451486613696</v>
       </c>
       <c r="D66">
-        <v>65.00766561136518</v>
+        <v>65.40951486613696</v>
       </c>
       <c r="E66">
-        <v>18.604</v>
+        <v>19.415</v>
       </c>
       <c r="F66">
-        <v>51.904</v>
+        <v>52.715</v>
       </c>
       <c r="G66">
         <v>25.8</v>
@@ -6821,28 +6821,28 @@
         <v>18.8</v>
       </c>
       <c r="M66">
-        <v>2.8183872</v>
+        <v>2.8624245</v>
       </c>
       <c r="N66">
-        <v>15.9816128</v>
+        <v>15.9375755</v>
       </c>
       <c r="O66">
-        <v>4.474851584</v>
+        <v>4.462521140000001</v>
       </c>
       <c r="P66">
-        <v>11.506761216</v>
+        <v>11.47505436</v>
       </c>
       <c r="Q66">
-        <v>21.806761216</v>
+        <v>21.77505436</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.140754580207478</v>
+        <v>0.1431343942477656</v>
       </c>
       <c r="T66">
-        <v>2.192946425114965</v>
+        <v>2.247907488401054</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.67048161444957</v>
+        <v>6.567858820381114</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07550943798671797</v>
+        <v>0.07532578709874388</v>
       </c>
       <c r="C67">
-        <v>38.49451486613696</v>
+        <v>38.0903631390364</v>
       </c>
       <c r="D67">
-        <v>65.40951486613696</v>
+        <v>65.8163631390364</v>
       </c>
       <c r="E67">
-        <v>19.415</v>
+        <v>20.226</v>
       </c>
       <c r="F67">
-        <v>52.715</v>
+        <v>53.526</v>
       </c>
       <c r="G67">
         <v>25.8</v>
@@ -6903,28 +6903,28 @@
         <v>18.8</v>
       </c>
       <c r="M67">
-        <v>2.8624245</v>
+        <v>2.9064618</v>
       </c>
       <c r="N67">
-        <v>15.9375755</v>
+        <v>15.8935382</v>
       </c>
       <c r="O67">
-        <v>4.462521140000001</v>
+        <v>4.450190696000001</v>
       </c>
       <c r="P67">
-        <v>11.47505436</v>
+        <v>11.443347504</v>
       </c>
       <c r="Q67">
-        <v>21.77505436</v>
+        <v>21.743347504</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1431343942477656</v>
+        <v>0.1456541973492467</v>
       </c>
       <c r="T67">
-        <v>2.247907488401054</v>
+        <v>2.306101555409855</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.567858820381114</v>
+        <v>6.468345807951098</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07532578709874388</v>
+        <v>0.07514213621076979</v>
       </c>
       <c r="C68">
-        <v>38.0903631390364</v>
+        <v>37.69130429583848</v>
       </c>
       <c r="D68">
-        <v>65.8163631390364</v>
+        <v>66.22830429583848</v>
       </c>
       <c r="E68">
-        <v>20.226</v>
+        <v>21.037</v>
       </c>
       <c r="F68">
-        <v>53.526</v>
+        <v>54.337</v>
       </c>
       <c r="G68">
         <v>25.8</v>
@@ -6985,28 +6985,28 @@
         <v>18.8</v>
       </c>
       <c r="M68">
-        <v>2.9064618</v>
+        <v>2.9504991</v>
       </c>
       <c r="N68">
-        <v>15.8935382</v>
+        <v>15.8495009</v>
       </c>
       <c r="O68">
-        <v>4.450190696000001</v>
+        <v>4.437860252000001</v>
       </c>
       <c r="P68">
-        <v>11.443347504</v>
+        <v>11.411640648</v>
       </c>
       <c r="Q68">
-        <v>21.743347504</v>
+        <v>21.711640648</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1456541973492467</v>
+        <v>0.1483267157902115</v>
       </c>
       <c r="T68">
-        <v>2.306101555409855</v>
+        <v>2.367822535570704</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.468345807951098</v>
+        <v>6.371803333205558</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07514213621076979</v>
+        <v>0.07495848532279568</v>
       </c>
       <c r="C69">
-        <v>37.69130429583848</v>
+        <v>37.29743456712323</v>
       </c>
       <c r="D69">
-        <v>66.22830429583848</v>
+        <v>66.64543456712323</v>
       </c>
       <c r="E69">
-        <v>21.037</v>
+        <v>21.84800000000001</v>
       </c>
       <c r="F69">
-        <v>54.337</v>
+        <v>55.148</v>
       </c>
       <c r="G69">
         <v>25.8</v>
@@ -7067,28 +7067,28 @@
         <v>18.8</v>
       </c>
       <c r="M69">
-        <v>2.9504991</v>
+        <v>2.9945364</v>
       </c>
       <c r="N69">
-        <v>15.8495009</v>
+        <v>15.8054636</v>
       </c>
       <c r="O69">
-        <v>4.437860252000001</v>
+        <v>4.425529808</v>
       </c>
       <c r="P69">
-        <v>11.411640648</v>
+        <v>11.379933792</v>
       </c>
       <c r="Q69">
-        <v>21.711640648</v>
+        <v>21.679933792</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1483267157902115</v>
+        <v>0.1511662666337365</v>
       </c>
       <c r="T69">
-        <v>2.367822535570704</v>
+        <v>2.433401076991606</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.371803333205558</v>
+        <v>6.278100343011358</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07495848532279568</v>
+        <v>0.07477483443482159</v>
       </c>
       <c r="C70">
-        <v>37.29743456712323</v>
+        <v>36.9088526232196</v>
       </c>
       <c r="D70">
-        <v>66.64543456712323</v>
+        <v>67.06785262321961</v>
       </c>
       <c r="E70">
-        <v>21.84800000000001</v>
+        <v>22.65900000000001</v>
       </c>
       <c r="F70">
-        <v>55.148</v>
+        <v>55.959</v>
       </c>
       <c r="G70">
         <v>25.8</v>
@@ -7149,28 +7149,28 @@
         <v>18.8</v>
       </c>
       <c r="M70">
-        <v>2.9945364</v>
+        <v>3.0385737</v>
       </c>
       <c r="N70">
-        <v>15.8054636</v>
+        <v>15.7614263</v>
       </c>
       <c r="O70">
-        <v>4.425529808</v>
+        <v>4.413199364</v>
       </c>
       <c r="P70">
-        <v>11.379933792</v>
+        <v>11.348226936</v>
       </c>
       <c r="Q70">
-        <v>21.679933792</v>
+        <v>21.648226936</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1511662666337365</v>
+        <v>0.1541890143058761</v>
       </c>
       <c r="T70">
-        <v>2.433401076991606</v>
+        <v>2.503210492052566</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.278100343011358</v>
+        <v>6.18711338151844</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07477483443482159</v>
+        <v>0.07509518354684749</v>
       </c>
       <c r="C71">
-        <v>36.9088526232196</v>
+        <v>35.36445127760337</v>
       </c>
       <c r="D71">
-        <v>67.06785262321961</v>
+        <v>66.33445127760338</v>
       </c>
       <c r="E71">
-        <v>22.65900000000001</v>
+        <v>23.47000000000001</v>
       </c>
       <c r="F71">
-        <v>55.959</v>
+        <v>56.77</v>
       </c>
       <c r="G71">
         <v>25.8</v>
@@ -7231,45 +7231,45 @@
         <v>18.8</v>
       </c>
       <c r="M71">
-        <v>3.0385737</v>
+        <v>3.139381</v>
       </c>
       <c r="N71">
-        <v>15.7614263</v>
+        <v>15.660619</v>
       </c>
       <c r="O71">
-        <v>4.413199364</v>
+        <v>4.38497332</v>
       </c>
       <c r="P71">
-        <v>11.348226936</v>
+        <v>11.27564568</v>
       </c>
       <c r="Q71">
-        <v>21.648226936</v>
+        <v>21.57564568</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1541890143058761</v>
+        <v>0.1574132784894917</v>
       </c>
       <c r="T71">
-        <v>2.503210492052566</v>
+        <v>2.577673868117591</v>
       </c>
       <c r="U71">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V71">
         <v>0.28</v>
       </c>
       <c r="W71">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>6.18711338151844</v>
+        <v>5.988441670507657</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07509518354684749</v>
+        <v>0.07491873265887339</v>
       </c>
       <c r="C72">
-        <v>35.36445127760337</v>
+        <v>34.95541838820293</v>
       </c>
       <c r="D72">
-        <v>66.33445127760338</v>
+        <v>66.73641838820294</v>
       </c>
       <c r="E72">
-        <v>23.47000000000001</v>
+        <v>24.28100000000001</v>
       </c>
       <c r="F72">
-        <v>56.77</v>
+        <v>57.581</v>
       </c>
       <c r="G72">
         <v>25.8</v>
@@ -7313,28 +7313,28 @@
         <v>18.8</v>
       </c>
       <c r="M72">
-        <v>3.139381</v>
+        <v>3.1842293</v>
       </c>
       <c r="N72">
-        <v>15.660619</v>
+        <v>15.6157707</v>
       </c>
       <c r="O72">
-        <v>4.38497332</v>
+        <v>4.372415796</v>
       </c>
       <c r="P72">
-        <v>11.27564568</v>
+        <v>11.243354904</v>
       </c>
       <c r="Q72">
-        <v>21.57564568</v>
+        <v>21.543354904</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1574132784894917</v>
+        <v>0.1608599057202531</v>
       </c>
       <c r="T72">
-        <v>2.577673868117591</v>
+        <v>2.657272649428479</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.988441670507657</v>
+        <v>5.904097421627267</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0749187326588734</v>
+        <v>0.0747422817708993</v>
       </c>
       <c r="C73">
-        <v>34.95541838820289</v>
+        <v>34.55128680231148</v>
       </c>
       <c r="D73">
-        <v>66.73641838820289</v>
+        <v>67.14328680231148</v>
       </c>
       <c r="E73">
-        <v>24.281</v>
+        <v>25.092</v>
       </c>
       <c r="F73">
-        <v>57.581</v>
+        <v>58.392</v>
       </c>
       <c r="G73">
         <v>25.8</v>
@@ -7395,28 +7395,28 @@
         <v>18.8</v>
       </c>
       <c r="M73">
-        <v>3.1842293</v>
+        <v>3.2290776</v>
       </c>
       <c r="N73">
-        <v>15.6157707</v>
+        <v>15.5709224</v>
       </c>
       <c r="O73">
-        <v>4.372415796</v>
+        <v>4.359858272</v>
       </c>
       <c r="P73">
-        <v>11.243354904</v>
+        <v>11.211064128</v>
       </c>
       <c r="Q73">
-        <v>21.543354904</v>
+        <v>21.511064128</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1608599057202531</v>
+        <v>0.1645527206103546</v>
       </c>
       <c r="T73">
-        <v>2.657272649428478</v>
+        <v>2.742557057975858</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.904097421627268</v>
+        <v>5.822096068549111</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0747422817708993</v>
+        <v>0.0745658308829252</v>
       </c>
       <c r="C74">
-        <v>34.55128680231148</v>
+        <v>34.15214671437122</v>
       </c>
       <c r="D74">
-        <v>67.14328680231148</v>
+        <v>67.55514671437122</v>
       </c>
       <c r="E74">
-        <v>25.092</v>
+        <v>25.903</v>
       </c>
       <c r="F74">
-        <v>58.392</v>
+        <v>59.203</v>
       </c>
       <c r="G74">
         <v>25.8</v>
@@ -7477,28 +7477,28 @@
         <v>18.8</v>
       </c>
       <c r="M74">
-        <v>3.2290776</v>
+        <v>3.2739259</v>
       </c>
       <c r="N74">
-        <v>15.5709224</v>
+        <v>15.5260741</v>
       </c>
       <c r="O74">
-        <v>4.359858272</v>
+        <v>4.347300748</v>
       </c>
       <c r="P74">
-        <v>11.211064128</v>
+        <v>11.178773352</v>
       </c>
       <c r="Q74">
-        <v>21.511064128</v>
+        <v>21.478773352</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1645527206103546</v>
+        <v>0.1685190773441674</v>
       </c>
       <c r="T74">
-        <v>2.742557057975858</v>
+        <v>2.83415883011934</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.822096068549111</v>
+        <v>5.742341327884056</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0745658308829252</v>
+        <v>0.0743893799949511</v>
       </c>
       <c r="C75">
-        <v>34.15214671437122</v>
+        <v>33.75809054550982</v>
       </c>
       <c r="D75">
-        <v>67.55514671437122</v>
+        <v>67.97209054550981</v>
       </c>
       <c r="E75">
-        <v>25.903</v>
+        <v>26.714</v>
       </c>
       <c r="F75">
-        <v>59.203</v>
+        <v>60.014</v>
       </c>
       <c r="G75">
         <v>25.8</v>
@@ -7559,28 +7559,28 @@
         <v>18.8</v>
       </c>
       <c r="M75">
-        <v>3.2739259</v>
+        <v>3.3187742</v>
       </c>
       <c r="N75">
-        <v>15.5260741</v>
+        <v>15.4812258</v>
       </c>
       <c r="O75">
-        <v>4.347300748</v>
+        <v>4.334743224</v>
       </c>
       <c r="P75">
-        <v>11.178773352</v>
+        <v>11.146482576</v>
       </c>
       <c r="Q75">
-        <v>21.478773352</v>
+        <v>21.446482576</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1685190773441674</v>
+        <v>0.1727905384421196</v>
       </c>
       <c r="T75">
-        <v>2.83415883011934</v>
+        <v>2.932806892427705</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.742341327884056</v>
+        <v>5.664742120750487</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0743893799949511</v>
+        <v>0.07421292910697702</v>
       </c>
       <c r="C76">
-        <v>33.75809054550982</v>
+        <v>33.36921301268145</v>
       </c>
       <c r="D76">
-        <v>67.97209054550981</v>
+        <v>68.39421301268145</v>
       </c>
       <c r="E76">
-        <v>26.714</v>
+        <v>27.525</v>
       </c>
       <c r="F76">
-        <v>60.014</v>
+        <v>60.825</v>
       </c>
       <c r="G76">
         <v>25.8</v>
@@ -7641,28 +7641,28 @@
         <v>18.8</v>
       </c>
       <c r="M76">
-        <v>3.3187742</v>
+        <v>3.3636225</v>
       </c>
       <c r="N76">
-        <v>15.4812258</v>
+        <v>15.4363775</v>
       </c>
       <c r="O76">
-        <v>4.334743224</v>
+        <v>4.3221857</v>
       </c>
       <c r="P76">
-        <v>11.146482576</v>
+        <v>11.1141918</v>
       </c>
       <c r="Q76">
-        <v>21.446482576</v>
+        <v>21.4141918</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1727905384421196</v>
+        <v>0.1774037164279081</v>
       </c>
       <c r="T76">
-        <v>2.932806892427705</v>
+        <v>3.039346799720741</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.664742120750487</v>
+        <v>5.589212225807147</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07421292910697702</v>
+        <v>0.07403647821900292</v>
       </c>
       <c r="C77">
-        <v>33.36921301268145</v>
+        <v>32.98561120040075</v>
       </c>
       <c r="D77">
-        <v>68.39421301268145</v>
+        <v>68.82161120040075</v>
       </c>
       <c r="E77">
-        <v>27.525</v>
+        <v>28.336</v>
       </c>
       <c r="F77">
-        <v>60.825</v>
+        <v>61.636</v>
       </c>
       <c r="G77">
         <v>25.8</v>
@@ -7723,28 +7723,28 @@
         <v>18.8</v>
       </c>
       <c r="M77">
-        <v>3.3636225</v>
+        <v>3.4084708</v>
       </c>
       <c r="N77">
-        <v>15.4363775</v>
+        <v>15.3915292</v>
       </c>
       <c r="O77">
-        <v>4.3221857</v>
+        <v>4.309628176</v>
       </c>
       <c r="P77">
-        <v>11.1141918</v>
+        <v>11.081901024</v>
       </c>
       <c r="Q77">
-        <v>21.4141918</v>
+        <v>21.381901024</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1774037164279081</v>
+        <v>0.1824013259125122</v>
       </c>
       <c r="T77">
-        <v>3.039346799720741</v>
+        <v>3.154765032621528</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.589212225807147</v>
+        <v>5.515669959678106</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07403647821900292</v>
+        <v>0.07386002733102882</v>
       </c>
       <c r="C78">
-        <v>32.98561120040075</v>
+        <v>32.60738463518249</v>
       </c>
       <c r="D78">
-        <v>68.82161120040075</v>
+        <v>69.25438463518249</v>
       </c>
       <c r="E78">
-        <v>28.336</v>
+        <v>29.147</v>
       </c>
       <c r="F78">
-        <v>61.636</v>
+        <v>62.447</v>
       </c>
       <c r="G78">
         <v>25.8</v>
@@ -7805,28 +7805,28 @@
         <v>18.8</v>
       </c>
       <c r="M78">
-        <v>3.4084708</v>
+        <v>3.4533191</v>
       </c>
       <c r="N78">
-        <v>15.3915292</v>
+        <v>15.3466809</v>
       </c>
       <c r="O78">
-        <v>4.309628176</v>
+        <v>4.297070652</v>
       </c>
       <c r="P78">
-        <v>11.081901024</v>
+        <v>11.049610248</v>
       </c>
       <c r="Q78">
-        <v>21.381901024</v>
+        <v>21.349610248</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1824013259125122</v>
+        <v>0.1878335101349079</v>
       </c>
       <c r="T78">
-        <v>3.154765032621528</v>
+        <v>3.280219633600645</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.515669959678106</v>
+        <v>5.444037882279689</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07386002733102882</v>
+        <v>0.07368357644305473</v>
       </c>
       <c r="C79">
-        <v>32.60738463518249</v>
+        <v>32.23463536280823</v>
       </c>
       <c r="D79">
-        <v>69.25438463518249</v>
+        <v>69.69263536280823</v>
       </c>
       <c r="E79">
-        <v>29.147</v>
+        <v>29.958</v>
       </c>
       <c r="F79">
-        <v>62.447</v>
+        <v>63.258</v>
       </c>
       <c r="G79">
         <v>25.8</v>
@@ -7887,28 +7887,28 @@
         <v>18.8</v>
       </c>
       <c r="M79">
-        <v>3.4533191</v>
+        <v>3.4981674</v>
       </c>
       <c r="N79">
-        <v>15.3466809</v>
+        <v>15.3018326</v>
       </c>
       <c r="O79">
-        <v>4.297070652</v>
+        <v>4.284513128</v>
       </c>
       <c r="P79">
-        <v>11.049610248</v>
+        <v>11.017319472</v>
       </c>
       <c r="Q79">
-        <v>21.349610248</v>
+        <v>21.317319472</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1878335101349079</v>
+        <v>0.1937595292866124</v>
       </c>
       <c r="T79">
-        <v>3.280219633600645</v>
+        <v>3.417079198305137</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.444037882279689</v>
+        <v>5.374242524814565</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07368357644305473</v>
+        <v>0.07350712555508063</v>
       </c>
       <c r="C80">
-        <v>32.23463536280823</v>
+        <v>31.8674680285453</v>
       </c>
       <c r="D80">
-        <v>69.69263536280823</v>
+        <v>70.13646802854531</v>
       </c>
       <c r="E80">
-        <v>29.958</v>
+        <v>30.76900000000001</v>
       </c>
       <c r="F80">
-        <v>63.258</v>
+        <v>64.069</v>
       </c>
       <c r="G80">
         <v>25.8</v>
@@ -7969,28 +7969,28 @@
         <v>18.8</v>
       </c>
       <c r="M80">
-        <v>3.4981674</v>
+        <v>3.5430157</v>
       </c>
       <c r="N80">
-        <v>15.3018326</v>
+        <v>15.2569843</v>
       </c>
       <c r="O80">
-        <v>4.284513128</v>
+        <v>4.271955604</v>
       </c>
       <c r="P80">
-        <v>11.017319472</v>
+        <v>10.985028696</v>
       </c>
       <c r="Q80">
-        <v>21.317319472</v>
+        <v>21.285028696</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1937595292866124</v>
+        <v>0.2002499312146697</v>
       </c>
       <c r="T80">
-        <v>3.417079198305137</v>
+        <v>3.566973007267199</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.374242524814565</v>
+        <v>5.306214138424506</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07350712555508063</v>
+        <v>0.07333067466710652</v>
       </c>
       <c r="C81">
-        <v>31.8674680285453</v>
+        <v>31.50598996045025</v>
       </c>
       <c r="D81">
-        <v>70.13646802854531</v>
+        <v>70.58598996045025</v>
       </c>
       <c r="E81">
-        <v>30.76900000000001</v>
+        <v>31.58</v>
       </c>
       <c r="F81">
-        <v>64.069</v>
+        <v>64.88</v>
       </c>
       <c r="G81">
         <v>25.8</v>
@@ -8051,28 +8051,28 @@
         <v>18.8</v>
       </c>
       <c r="M81">
-        <v>3.5430157</v>
+        <v>3.587864</v>
       </c>
       <c r="N81">
-        <v>15.2569843</v>
+        <v>15.212136</v>
       </c>
       <c r="O81">
-        <v>4.271955604</v>
+        <v>4.25939808</v>
       </c>
       <c r="P81">
-        <v>10.985028696</v>
+        <v>10.95273792</v>
       </c>
       <c r="Q81">
-        <v>21.285028696</v>
+        <v>21.25273792</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2002499312146697</v>
+        <v>0.2073893733355327</v>
       </c>
       <c r="T81">
-        <v>3.566973007267199</v>
+        <v>3.731856197125467</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.306214138424506</v>
+        <v>5.2398864616942</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07333067466710652</v>
+        <v>0.07315422377913244</v>
       </c>
       <c r="C82">
-        <v>31.50598996045025</v>
+        <v>31.15031125589685</v>
       </c>
       <c r="D82">
-        <v>70.58598996045025</v>
+        <v>71.04131125589686</v>
       </c>
       <c r="E82">
-        <v>31.58</v>
+        <v>32.39100000000001</v>
       </c>
       <c r="F82">
-        <v>64.88</v>
+        <v>65.691</v>
       </c>
       <c r="G82">
         <v>25.8</v>
@@ -8133,28 +8133,28 @@
         <v>18.8</v>
       </c>
       <c r="M82">
-        <v>3.587864</v>
+        <v>3.6327123</v>
       </c>
       <c r="N82">
-        <v>15.212136</v>
+        <v>15.1672877</v>
       </c>
       <c r="O82">
-        <v>4.25939808</v>
+        <v>4.246840556</v>
       </c>
       <c r="P82">
-        <v>10.95273792</v>
+        <v>10.920447144</v>
       </c>
       <c r="Q82">
-        <v>21.25273792</v>
+        <v>21.220447144</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2073893733355327</v>
+        <v>0.2152803356796444</v>
       </c>
       <c r="T82">
-        <v>3.731856197125467</v>
+        <v>3.914095512231973</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.2398864616942</v>
+        <v>5.175196505376988</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07315422377913244</v>
+        <v>0.07297777289115834</v>
       </c>
       <c r="C83">
-        <v>31.15031125589685</v>
+        <v>30.8005448714749</v>
       </c>
       <c r="D83">
-        <v>71.04131125589686</v>
+        <v>71.5025448714749</v>
       </c>
       <c r="E83">
-        <v>32.39100000000001</v>
+        <v>33.202</v>
       </c>
       <c r="F83">
-        <v>65.691</v>
+        <v>66.502</v>
       </c>
       <c r="G83">
         <v>25.8</v>
@@ -8215,28 +8215,28 @@
         <v>18.8</v>
       </c>
       <c r="M83">
-        <v>3.6327123</v>
+        <v>3.6775606</v>
       </c>
       <c r="N83">
-        <v>15.1672877</v>
+        <v>15.1224394</v>
       </c>
       <c r="O83">
-        <v>4.246840556</v>
+        <v>4.234283032</v>
       </c>
       <c r="P83">
-        <v>10.920447144</v>
+        <v>10.888156368</v>
       </c>
       <c r="Q83">
-        <v>21.220447144</v>
+        <v>21.188156368</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2152803356796444</v>
+        <v>0.2240480716175464</v>
       </c>
       <c r="T83">
-        <v>3.914095512231973</v>
+        <v>4.116583640128093</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.175196505376988</v>
+        <v>5.11208435287239</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07297777289115834</v>
+        <v>0.07280132200318425</v>
       </c>
       <c r="C84">
-        <v>30.8005448714749</v>
+        <v>30.45680671641313</v>
       </c>
       <c r="D84">
-        <v>71.5025448714749</v>
+        <v>71.96980671641313</v>
       </c>
       <c r="E84">
-        <v>33.202</v>
+        <v>34.01300000000001</v>
       </c>
       <c r="F84">
-        <v>66.502</v>
+        <v>67.313</v>
       </c>
       <c r="G84">
         <v>25.8</v>
@@ -8297,28 +8297,28 @@
         <v>18.8</v>
       </c>
       <c r="M84">
-        <v>3.6775606</v>
+        <v>3.7224089</v>
       </c>
       <c r="N84">
-        <v>15.1224394</v>
+        <v>15.0775911</v>
       </c>
       <c r="O84">
-        <v>4.234283032</v>
+        <v>4.221725508</v>
       </c>
       <c r="P84">
-        <v>10.888156368</v>
+        <v>10.855865592</v>
       </c>
       <c r="Q84">
-        <v>21.188156368</v>
+        <v>21.155865592</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2240480716175464</v>
+        <v>0.2338473059010839</v>
       </c>
       <c r="T84">
-        <v>4.116583640128093</v>
+        <v>4.342893900717873</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.11208435287239</v>
+        <v>5.050492975126939</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07280132200318425</v>
+        <v>0.07262487111521015</v>
       </c>
       <c r="C85">
-        <v>30.45680671641313</v>
+        <v>30.11921574969026</v>
       </c>
       <c r="D85">
-        <v>71.96980671641313</v>
+        <v>72.44321574969025</v>
       </c>
       <c r="E85">
-        <v>34.01300000000001</v>
+        <v>34.824</v>
       </c>
       <c r="F85">
-        <v>67.313</v>
+        <v>68.124</v>
       </c>
       <c r="G85">
         <v>25.8</v>
@@ -8379,28 +8379,28 @@
         <v>18.8</v>
       </c>
       <c r="M85">
-        <v>3.7224089</v>
+        <v>3.7672572</v>
       </c>
       <c r="N85">
-        <v>15.0775911</v>
+        <v>15.0327428</v>
       </c>
       <c r="O85">
-        <v>4.221725508</v>
+        <v>4.209167984</v>
       </c>
       <c r="P85">
-        <v>10.855865592</v>
+        <v>10.823574816</v>
       </c>
       <c r="Q85">
-        <v>21.155865592</v>
+        <v>21.123574816</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2338473059010839</v>
+        <v>0.2448714444700636</v>
       </c>
       <c r="T85">
-        <v>4.342893900717873</v>
+        <v>4.597492943881377</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.050492975126939</v>
+        <v>4.990368058756381</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07262487111521015</v>
+        <v>0.07244842022723605</v>
       </c>
       <c r="C86">
-        <v>30.11921574969026</v>
+        <v>29.78789408100342</v>
       </c>
       <c r="D86">
-        <v>72.44321574969025</v>
+        <v>72.92289408100341</v>
       </c>
       <c r="E86">
-        <v>34.824</v>
+        <v>35.63499999999999</v>
       </c>
       <c r="F86">
-        <v>68.124</v>
+        <v>68.93499999999999</v>
       </c>
       <c r="G86">
         <v>25.8</v>
@@ -8461,28 +8461,28 @@
         <v>18.8</v>
       </c>
       <c r="M86">
-        <v>3.7672572</v>
+        <v>3.812105499999999</v>
       </c>
       <c r="N86">
-        <v>15.0327428</v>
+        <v>14.9878945</v>
       </c>
       <c r="O86">
-        <v>4.209167984</v>
+        <v>4.19661046</v>
       </c>
       <c r="P86">
-        <v>10.823574816</v>
+        <v>10.79128404</v>
       </c>
       <c r="Q86">
-        <v>21.123574816</v>
+        <v>21.09128404</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2448714444700635</v>
+        <v>0.2573654681815737</v>
       </c>
       <c r="T86">
-        <v>4.597492943881373</v>
+        <v>4.886038526133341</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.990368058756381</v>
+        <v>4.931657846300425</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07244842022723605</v>
+        <v>0.07227196933926196</v>
       </c>
       <c r="C87">
-        <v>29.78789408100342</v>
+        <v>29.46296707577488</v>
       </c>
       <c r="D87">
-        <v>72.92289408100341</v>
+        <v>73.40896707577488</v>
       </c>
       <c r="E87">
-        <v>35.63499999999999</v>
+        <v>36.446</v>
       </c>
       <c r="F87">
-        <v>68.93499999999999</v>
+        <v>69.746</v>
       </c>
       <c r="G87">
         <v>25.8</v>
@@ -8543,28 +8543,28 @@
         <v>18.8</v>
       </c>
       <c r="M87">
-        <v>3.812105499999999</v>
+        <v>3.8569538</v>
       </c>
       <c r="N87">
-        <v>14.9878945</v>
+        <v>14.9430462</v>
       </c>
       <c r="O87">
-        <v>4.19661046</v>
+        <v>4.184052936</v>
       </c>
       <c r="P87">
-        <v>10.79128404</v>
+        <v>10.758993264</v>
       </c>
       <c r="Q87">
-        <v>21.09128404</v>
+        <v>21.058993264</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2573654681815737</v>
+        <v>0.2716443524232997</v>
       </c>
       <c r="T87">
-        <v>4.886038526133341</v>
+        <v>5.215804905849878</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.931657846300425</v>
+        <v>4.874312987622512</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07227196933926196</v>
+        <v>0.07209551845128787</v>
       </c>
       <c r="C88">
-        <v>29.46296707577488</v>
+        <v>29.14456346438676</v>
       </c>
       <c r="D88">
-        <v>73.40896707577488</v>
+        <v>73.90156346438675</v>
       </c>
       <c r="E88">
-        <v>36.446</v>
+        <v>37.25699999999999</v>
       </c>
       <c r="F88">
-        <v>69.746</v>
+        <v>70.55699999999999</v>
       </c>
       <c r="G88">
         <v>25.8</v>
@@ -8625,28 +8625,28 @@
         <v>18.8</v>
       </c>
       <c r="M88">
-        <v>3.8569538</v>
+        <v>3.901802099999999</v>
       </c>
       <c r="N88">
-        <v>14.9430462</v>
+        <v>14.8981979</v>
       </c>
       <c r="O88">
-        <v>4.184052936</v>
+        <v>4.171495412000001</v>
       </c>
       <c r="P88">
-        <v>10.758993264</v>
+        <v>10.726702488</v>
       </c>
       <c r="Q88">
-        <v>21.058993264</v>
+        <v>21.026702488</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2716443524232997</v>
+        <v>0.2881199880868297</v>
       </c>
       <c r="T88">
-        <v>5.215804905849878</v>
+        <v>5.596304574753573</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.874312987622512</v>
+        <v>4.818286401557886</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07209551845128787</v>
+        <v>0.07191906756331377</v>
       </c>
       <c r="C89">
-        <v>29.14456346438676</v>
+        <v>28.832815455843</v>
       </c>
       <c r="D89">
-        <v>73.90156346438675</v>
+        <v>74.400815455843</v>
       </c>
       <c r="E89">
-        <v>37.25699999999999</v>
+        <v>38.068</v>
       </c>
       <c r="F89">
-        <v>70.55699999999999</v>
+        <v>71.36799999999999</v>
       </c>
       <c r="G89">
         <v>25.8</v>
@@ -8707,28 +8707,28 @@
         <v>18.8</v>
       </c>
       <c r="M89">
-        <v>3.901802099999999</v>
+        <v>3.9466504</v>
       </c>
       <c r="N89">
-        <v>14.8981979</v>
+        <v>14.8533496</v>
       </c>
       <c r="O89">
-        <v>4.171495412000001</v>
+        <v>4.158937888000001</v>
       </c>
       <c r="P89">
-        <v>10.726702488</v>
+        <v>10.694411712</v>
       </c>
       <c r="Q89">
-        <v>21.026702488</v>
+        <v>20.994411712</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2881199880868297</v>
+        <v>0.3073415630276148</v>
       </c>
       <c r="T89">
-        <v>5.596304574753573</v>
+        <v>6.040220855141219</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.818286401557886</v>
+        <v>4.763533146994728</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07191906756331377</v>
+        <v>0.07174261667533968</v>
       </c>
       <c r="C90">
-        <v>28.832815455843</v>
+        <v>28.5278588560702</v>
       </c>
       <c r="D90">
-        <v>74.400815455843</v>
+        <v>74.9068588560702</v>
       </c>
       <c r="E90">
-        <v>38.068</v>
+        <v>38.879</v>
       </c>
       <c r="F90">
-        <v>71.36799999999999</v>
+        <v>72.179</v>
       </c>
       <c r="G90">
         <v>25.8</v>
@@ -8789,28 +8789,28 @@
         <v>18.8</v>
       </c>
       <c r="M90">
-        <v>3.9466504</v>
+        <v>3.9914987</v>
       </c>
       <c r="N90">
-        <v>14.8533496</v>
+        <v>14.8085013</v>
       </c>
       <c r="O90">
-        <v>4.158937888000001</v>
+        <v>4.146380364000001</v>
       </c>
       <c r="P90">
-        <v>10.694411712</v>
+        <v>10.662120936</v>
       </c>
       <c r="Q90">
-        <v>20.994411712</v>
+        <v>20.962120936</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3073415630276148</v>
+        <v>0.3300579697758153</v>
       </c>
       <c r="T90">
-        <v>6.040220855141219</v>
+        <v>6.564849186508436</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.763533146994728</v>
+        <v>4.710010302646472</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07174261667533968</v>
+        <v>0.07156616578736558</v>
       </c>
       <c r="C91">
-        <v>28.5278588560702</v>
+        <v>28.22983319107918</v>
       </c>
       <c r="D91">
-        <v>74.9068588560702</v>
+        <v>75.41983319107918</v>
       </c>
       <c r="E91">
-        <v>38.879</v>
+        <v>39.69</v>
       </c>
       <c r="F91">
-        <v>72.179</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="G91">
         <v>25.8</v>
@@ -8871,28 +8871,28 @@
         <v>18.8</v>
       </c>
       <c r="M91">
-        <v>3.9914987</v>
+        <v>4.036347</v>
       </c>
       <c r="N91">
-        <v>14.8085013</v>
+        <v>14.763653</v>
       </c>
       <c r="O91">
-        <v>4.146380364000001</v>
+        <v>4.133822840000001</v>
       </c>
       <c r="P91">
-        <v>10.662120936</v>
+        <v>10.62983016</v>
       </c>
       <c r="Q91">
-        <v>20.962120936</v>
+        <v>20.92983016</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3300579697758153</v>
+        <v>0.3573176578736559</v>
       </c>
       <c r="T91">
-        <v>6.564849186508436</v>
+        <v>7.194403184149096</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.710010302646472</v>
+        <v>4.65767685483929</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07156616578736558</v>
+        <v>0.07138971489939147</v>
       </c>
       <c r="C92">
-        <v>28.22983319107918</v>
+        <v>27.93888183522179</v>
       </c>
       <c r="D92">
-        <v>75.41983319107918</v>
+        <v>75.9398818352218</v>
       </c>
       <c r="E92">
-        <v>39.69</v>
+        <v>40.501</v>
       </c>
       <c r="F92">
-        <v>72.98999999999999</v>
+        <v>73.801</v>
       </c>
       <c r="G92">
         <v>25.8</v>
@@ -8953,28 +8953,28 @@
         <v>18.8</v>
       </c>
       <c r="M92">
-        <v>4.036347</v>
+        <v>4.0811953</v>
       </c>
       <c r="N92">
-        <v>14.763653</v>
+        <v>14.7188047</v>
       </c>
       <c r="O92">
-        <v>4.133822840000001</v>
+        <v>4.121265316000001</v>
       </c>
       <c r="P92">
-        <v>10.62983016</v>
+        <v>10.597539384</v>
       </c>
       <c r="Q92">
-        <v>20.92983016</v>
+        <v>20.897539384</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3573176578736559</v>
+        <v>0.3906350544376832</v>
       </c>
       <c r="T92">
-        <v>7.194403184149096</v>
+        <v>7.963858070154346</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.65767685483929</v>
+        <v>4.606493592698198</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07138971489939147</v>
+        <v>0.07121326401141739</v>
       </c>
       <c r="C93">
-        <v>27.93888183522179</v>
+        <v>27.6551521447913</v>
       </c>
       <c r="D93">
-        <v>75.9398818352218</v>
+        <v>76.4671521447913</v>
       </c>
       <c r="E93">
-        <v>40.501</v>
+        <v>41.312</v>
       </c>
       <c r="F93">
-        <v>73.801</v>
+        <v>74.61199999999999</v>
       </c>
       <c r="G93">
         <v>25.8</v>
@@ -9035,28 +9035,28 @@
         <v>18.8</v>
       </c>
       <c r="M93">
-        <v>4.0811953</v>
+        <v>4.1260436</v>
       </c>
       <c r="N93">
-        <v>14.7188047</v>
+        <v>14.6739564</v>
       </c>
       <c r="O93">
-        <v>4.121265316000001</v>
+        <v>4.108707792000001</v>
       </c>
       <c r="P93">
-        <v>10.597539384</v>
+        <v>10.565248608</v>
       </c>
       <c r="Q93">
-        <v>20.897539384</v>
+        <v>20.865248608</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3906350544376832</v>
+        <v>0.4322818001427176</v>
       </c>
       <c r="T93">
-        <v>7.963858070154346</v>
+        <v>8.925676677660913</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.606493592698198</v>
+        <v>4.556423010168871</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07121326401141739</v>
+        <v>0.07103681312344329</v>
       </c>
       <c r="C94">
-        <v>27.6551521447913</v>
+        <v>27.37879559722728</v>
       </c>
       <c r="D94">
-        <v>76.4671521447913</v>
+        <v>77.00179559722729</v>
       </c>
       <c r="E94">
-        <v>41.312</v>
+        <v>42.123</v>
       </c>
       <c r="F94">
-        <v>74.61199999999999</v>
+        <v>75.423</v>
       </c>
       <c r="G94">
         <v>25.8</v>
@@ -9117,28 +9117,28 @@
         <v>18.8</v>
       </c>
       <c r="M94">
-        <v>4.1260436</v>
+        <v>4.1708919</v>
       </c>
       <c r="N94">
-        <v>14.6739564</v>
+        <v>14.6291081</v>
       </c>
       <c r="O94">
-        <v>4.108707792000001</v>
+        <v>4.096150268000001</v>
       </c>
       <c r="P94">
-        <v>10.565248608</v>
+        <v>10.532957832</v>
       </c>
       <c r="Q94">
-        <v>20.865248608</v>
+        <v>20.832957832</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4322818001427176</v>
+        <v>0.4858276160491902</v>
       </c>
       <c r="T94">
-        <v>8.925676677660913</v>
+        <v>10.16230060159793</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.556423010168871</v>
+        <v>4.507429214360602</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07103681312344329</v>
+        <v>0.07255236223546918</v>
       </c>
       <c r="C95">
-        <v>27.37879559722728</v>
+        <v>22.20556388420673</v>
       </c>
       <c r="D95">
-        <v>77.00179559722729</v>
+        <v>72.63956388420672</v>
       </c>
       <c r="E95">
-        <v>42.123</v>
+        <v>42.934</v>
       </c>
       <c r="F95">
-        <v>75.423</v>
+        <v>76.23399999999999</v>
       </c>
       <c r="G95">
         <v>25.8</v>
@@ -9199,45 +9199,45 @@
         <v>18.8</v>
       </c>
       <c r="M95">
-        <v>4.1708919</v>
+        <v>4.4063252</v>
       </c>
       <c r="N95">
-        <v>14.6291081</v>
+        <v>14.3936748</v>
       </c>
       <c r="O95">
-        <v>4.096150268000001</v>
+        <v>4.030228944</v>
       </c>
       <c r="P95">
-        <v>10.532957832</v>
+        <v>10.363445856</v>
       </c>
       <c r="Q95">
-        <v>20.832957832</v>
+        <v>20.663445856</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4858276160491902</v>
+        <v>0.5572220372578203</v>
       </c>
       <c r="T95">
-        <v>10.16230060159793</v>
+        <v>11.81113250018061</v>
       </c>
       <c r="U95">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V95">
         <v>0.28</v>
       </c>
       <c r="W95">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>4.507429214360602</v>
+        <v>4.266593850131624</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07255236223546918</v>
+        <v>0.07239391134749509</v>
       </c>
       <c r="C96">
-        <v>22.20556388420673</v>
+        <v>21.82736232626768</v>
       </c>
       <c r="D96">
-        <v>72.63956388420672</v>
+        <v>73.07236232626768</v>
       </c>
       <c r="E96">
-        <v>42.934</v>
+        <v>43.745</v>
       </c>
       <c r="F96">
-        <v>76.23399999999999</v>
+        <v>77.045</v>
       </c>
       <c r="G96">
         <v>25.8</v>
@@ -9281,28 +9281,28 @@
         <v>18.8</v>
       </c>
       <c r="M96">
-        <v>4.4063252</v>
+        <v>4.453201000000001</v>
       </c>
       <c r="N96">
-        <v>14.3936748</v>
+        <v>14.346799</v>
       </c>
       <c r="O96">
-        <v>4.030228944</v>
+        <v>4.017103720000001</v>
       </c>
       <c r="P96">
-        <v>10.363445856</v>
+        <v>10.32969528</v>
       </c>
       <c r="Q96">
-        <v>20.663445856</v>
+        <v>20.62969528</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5572220372578203</v>
+        <v>0.6571742269499028</v>
       </c>
       <c r="T96">
-        <v>11.81113250018061</v>
+        <v>14.11949715819637</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.266593850131624</v>
+        <v>4.221682335919712</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07239391134749509</v>
+        <v>0.07223546045952101</v>
       </c>
       <c r="C97">
-        <v>21.82736232626768</v>
+        <v>21.4543490492412</v>
       </c>
       <c r="D97">
-        <v>73.07236232626768</v>
+        <v>73.5103490492412</v>
       </c>
       <c r="E97">
-        <v>43.745</v>
+        <v>44.556</v>
       </c>
       <c r="F97">
-        <v>77.045</v>
+        <v>77.85599999999999</v>
       </c>
       <c r="G97">
         <v>25.8</v>
@@ -9363,28 +9363,28 @@
         <v>18.8</v>
       </c>
       <c r="M97">
-        <v>4.453201000000001</v>
+        <v>4.5000768</v>
       </c>
       <c r="N97">
-        <v>14.346799</v>
+        <v>14.2999232</v>
       </c>
       <c r="O97">
-        <v>4.017103720000001</v>
+        <v>4.003978496</v>
       </c>
       <c r="P97">
-        <v>10.32969528</v>
+        <v>10.295944704</v>
       </c>
       <c r="Q97">
-        <v>20.62969528</v>
+        <v>20.595944704</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6571742269499028</v>
+        <v>0.8071025114880264</v>
       </c>
       <c r="T97">
-        <v>14.11949715819637</v>
+        <v>17.58204414522001</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.221682335919712</v>
+        <v>4.177706478253882</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07223546045952101</v>
+        <v>0.0720770095715469</v>
       </c>
       <c r="C98">
-        <v>21.4543490492412</v>
+        <v>21.08661790943718</v>
       </c>
       <c r="D98">
-        <v>73.5103490492412</v>
+        <v>73.95361790943717</v>
       </c>
       <c r="E98">
-        <v>44.556</v>
+        <v>45.36699999999999</v>
       </c>
       <c r="F98">
-        <v>77.85599999999999</v>
+        <v>78.66699999999999</v>
       </c>
       <c r="G98">
         <v>25.8</v>
@@ -9445,28 +9445,28 @@
         <v>18.8</v>
       </c>
       <c r="M98">
-        <v>4.5000768</v>
+        <v>4.5469526</v>
       </c>
       <c r="N98">
-        <v>14.2999232</v>
+        <v>14.2530474</v>
       </c>
       <c r="O98">
-        <v>4.003978496</v>
+        <v>3.990853272</v>
       </c>
       <c r="P98">
-        <v>10.295944704</v>
+        <v>10.262194128</v>
       </c>
       <c r="Q98">
-        <v>20.595944704</v>
+        <v>20.562194128</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8071025114880244</v>
+        <v>1.056982985718229</v>
       </c>
       <c r="T98">
-        <v>17.58204414521996</v>
+        <v>23.35295579025934</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.177706478253882</v>
+        <v>4.134637339302811</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0720770095715469</v>
+        <v>0.07191855868357282</v>
       </c>
       <c r="C99">
-        <v>21.08661790943718</v>
+        <v>20.72426504072075</v>
       </c>
       <c r="D99">
-        <v>73.95361790943717</v>
+        <v>74.40226504072075</v>
       </c>
       <c r="E99">
-        <v>45.36699999999999</v>
+        <v>46.178</v>
       </c>
       <c r="F99">
-        <v>78.66699999999999</v>
+        <v>79.47799999999999</v>
       </c>
       <c r="G99">
         <v>25.8</v>
@@ -9527,28 +9527,28 @@
         <v>18.8</v>
       </c>
       <c r="M99">
-        <v>4.5469526</v>
+        <v>4.5938284</v>
       </c>
       <c r="N99">
-        <v>14.2530474</v>
+        <v>14.2061716</v>
       </c>
       <c r="O99">
-        <v>3.990853272</v>
+        <v>3.977728048000001</v>
       </c>
       <c r="P99">
-        <v>10.262194128</v>
+        <v>10.228443552</v>
       </c>
       <c r="Q99">
-        <v>20.562194128</v>
+        <v>20.528443552</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.056982985718229</v>
+        <v>1.556743934178639</v>
       </c>
       <c r="T99">
-        <v>23.35295579025934</v>
+        <v>34.89477908033809</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.134637339302811</v>
+        <v>4.092447162371151</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07191855868357282</v>
+        <v>0.07176010779559872</v>
       </c>
       <c r="C100">
-        <v>20.72426504072075</v>
+        <v>20.36738892401932</v>
       </c>
       <c r="D100">
-        <v>74.40226504072075</v>
+        <v>74.85638892401931</v>
       </c>
       <c r="E100">
-        <v>46.178</v>
+        <v>46.98899999999999</v>
       </c>
       <c r="F100">
-        <v>79.47799999999999</v>
+        <v>80.28899999999999</v>
       </c>
       <c r="G100">
         <v>25.8</v>
@@ -9609,28 +9609,28 @@
         <v>18.8</v>
       </c>
       <c r="M100">
-        <v>4.5938284</v>
+        <v>4.640704199999999</v>
       </c>
       <c r="N100">
-        <v>14.2061716</v>
+        <v>14.1592958</v>
       </c>
       <c r="O100">
-        <v>3.977728048000001</v>
+        <v>3.964602824000001</v>
       </c>
       <c r="P100">
-        <v>10.228443552</v>
+        <v>10.194692976</v>
       </c>
       <c r="Q100">
-        <v>20.528443552</v>
+        <v>20.494692976</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.556743934178639</v>
+        <v>3.056026779559869</v>
       </c>
       <c r="T100">
-        <v>34.89477908033809</v>
+        <v>69.52024895057434</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.092447162371151</v>
+        <v>4.05110931224619</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07176010779559872</v>
-      </c>
-      <c r="C101">
-        <v>20.36738892401932</v>
-      </c>
-      <c r="D101">
-        <v>74.85638892401931</v>
-      </c>
-      <c r="E101">
-        <v>46.98899999999999</v>
-      </c>
-      <c r="F101">
-        <v>80.28899999999999</v>
-      </c>
-      <c r="G101">
-        <v>25.8</v>
-      </c>
-      <c r="H101">
-        <v>47.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>29.1</v>
-      </c>
-      <c r="K101">
-        <v>10.3</v>
-      </c>
-      <c r="L101">
-        <v>18.8</v>
-      </c>
-      <c r="M101">
-        <v>4.640704199999999</v>
-      </c>
-      <c r="N101">
-        <v>14.1592958</v>
-      </c>
-      <c r="O101">
-        <v>3.964602824000001</v>
-      </c>
-      <c r="P101">
-        <v>10.194692976</v>
-      </c>
-      <c r="Q101">
-        <v>20.494692976</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.056026779559869</v>
-      </c>
-      <c r="T101">
-        <v>69.52024895057434</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.28</v>
-      </c>
-      <c r="W101">
-        <v>0.041616</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.05110931224619</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
